--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss\Documents\repos\behaviour_rig\Params\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C0A6C2-1B92-42F3-9578-C5846B467527}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78227AEB-11A2-46F8-804E-D68F90745DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26400" yWindow="4230" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="352" uniqueCount="108">
   <si>
     <t>Subject</t>
   </si>
@@ -89,9 +89,6 @@
     <t>Arduino</t>
   </si>
   <si>
-    <t>Asym_Left</t>
-  </si>
-  <si>
     <t>Unilateral_Right</t>
   </si>
   <si>
@@ -233,9 +230,6 @@
     <t>SS01</t>
   </si>
   <si>
-    <t>SS02</t>
-  </si>
-  <si>
     <t>SS04</t>
   </si>
   <si>
@@ -324,6 +318,48 @@
   </si>
   <si>
     <t>Anti_Only</t>
+  </si>
+  <si>
+    <t>Habituation</t>
+  </si>
+  <si>
+    <t>TEST_Habi</t>
+  </si>
+  <si>
+    <t>TEST_Lick</t>
+  </si>
+  <si>
+    <t>TEST_3N3</t>
+  </si>
+  <si>
+    <t>Lick_To_Release</t>
+  </si>
+  <si>
+    <t>SS05</t>
+  </si>
+  <si>
+    <t>SS06</t>
+  </si>
+  <si>
+    <t>SS07</t>
+  </si>
+  <si>
+    <t>SS08</t>
+  </si>
+  <si>
+    <t>SS09</t>
+  </si>
+  <si>
+    <t>SS10</t>
+  </si>
+  <si>
+    <t>SS11</t>
+  </si>
+  <si>
+    <t>SS12</t>
+  </si>
+  <si>
+    <t>SS13</t>
   </si>
 </sst>
 </file>
@@ -707,7 +743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW36"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -752,7 +788,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>3</v>
@@ -770,94 +806,94 @@
         <v>7</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="O1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="P1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="S1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="Y1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Y1" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="Z1" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AA1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AB1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AC1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="AC1" s="1" t="s">
-        <v>50</v>
-      </c>
       <c r="AD1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="AF1" s="1" t="s">
-        <v>53</v>
-      </c>
       <c r="AG1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="AH1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AI1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="AK1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="AL1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AM1" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>13</v>
@@ -866,204 +902,194 @@
         <v>14</v>
       </c>
       <c r="AP1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AQ1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="AT1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="48" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
       <c r="B2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="D2" t="e">
-        <f>#N/A</f>
-        <v>#N/A</v>
-      </c>
-      <c r="E2" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
+        <v>#N/A</v>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2">
-        <v>8</v>
-      </c>
-      <c r="I2" t="str">
-        <f t="shared" ref="I2:J2" si="0">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="J2" t="str">
-        <f t="shared" si="0"/>
-        <v>False</v>
+      <c r="H2">
+        <v>2</v>
+      </c>
+      <c r="I2" t="b">
+        <v>0</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
       </c>
       <c r="K2" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" t="s">
-        <v>30</v>
-      </c>
       <c r="M2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N2" s="3">
-        <v>300</v>
-      </c>
-      <c r="O2" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="P2" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>30</v>
-      </c>
-      <c r="R2" s="3">
-        <v>1</v>
-      </c>
-      <c r="S2" t="str">
-        <f t="shared" ref="S2" si="1">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="T2" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U2" s="3">
+        <v>54</v>
+      </c>
+      <c r="N2">
+        <v>300</v>
+      </c>
+      <c r="O2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>30</v>
+      </c>
+      <c r="R2">
+        <v>1.75</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <v>0.8</v>
+      </c>
+      <c r="U2">
         <v>0.5</v>
       </c>
-      <c r="V2" t="str">
-        <f t="shared" ref="V2" si="2">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="W2" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X2" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y2" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z2" s="3">
-        <v>2</v>
-      </c>
-      <c r="AA2" s="3">
-        <v>5</v>
-      </c>
-      <c r="AB2" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC2" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD2" s="3">
+      <c r="V2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.8</v>
+      </c>
+      <c r="X2">
+        <v>50</v>
+      </c>
+      <c r="Y2">
+        <v>50</v>
+      </c>
+      <c r="Z2">
+        <v>10</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
+      <c r="AB2">
+        <v>10</v>
+      </c>
+      <c r="AC2">
+        <v>50</v>
+      </c>
+      <c r="AD2">
         <v>82</v>
       </c>
-      <c r="AE2" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF2" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG2" t="str">
-        <f>PROPER(TRUE)</f>
-        <v>True</v>
-      </c>
-      <c r="AH2" s="3">
+      <c r="AE2">
+        <v>300</v>
+      </c>
+      <c r="AF2">
+        <v>30</v>
+      </c>
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2">
         <v>20</v>
       </c>
-      <c r="AI2" s="3">
-        <v>2</v>
-      </c>
-      <c r="AJ2" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK2" t="str">
-        <f t="shared" ref="AK2" si="3">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="AL2" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="AM2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN2" s="5">
-        <v>30</v>
-      </c>
-      <c r="AO2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="AQ2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="AS2" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="AT2" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU2" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="AV2" s="5" t="s">
-        <v>63</v>
+      <c r="AI2">
+        <v>3</v>
+      </c>
+      <c r="AJ2">
+        <v>0.8</v>
+      </c>
+      <c r="AK2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU2" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV2" t="e">
+        <v>#N/A</v>
       </c>
       <c r="AW2" t="e">
-        <f>#N/A</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>98</v>
       </c>
       <c r="D3" t="e">
         <v>#N/A</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
         <v>10</v>
@@ -1071,8 +1097,8 @@
       <c r="G3" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="2">
-        <v>8</v>
+      <c r="H3">
+        <v>2</v>
       </c>
       <c r="I3" t="b">
         <v>0</v>
@@ -1081,13 +1107,13 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" t="s">
-        <v>30</v>
-      </c>
       <c r="M3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N3">
         <v>300</v>
@@ -1102,7 +1128,7 @@
         <v>30</v>
       </c>
       <c r="R3">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="S3" t="b">
         <v>0</v>
@@ -1200,19 +1226,19 @@
     </row>
     <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="D4" t="e">
         <v>#N/A</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -1220,8 +1246,8 @@
       <c r="G4" t="s">
         <v>9</v>
       </c>
-      <c r="H4" s="2">
-        <v>8</v>
+      <c r="H4">
+        <v>2</v>
       </c>
       <c r="I4" t="b">
         <v>0</v>
@@ -1230,13 +1256,13 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
+        <v>28</v>
+      </c>
+      <c r="L4" t="s">
         <v>29</v>
       </c>
-      <c r="L4" t="s">
-        <v>30</v>
-      </c>
       <c r="M4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N4">
         <v>300</v>
@@ -1251,7 +1277,7 @@
         <v>30</v>
       </c>
       <c r="R4">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="S4" t="b">
         <v>0</v>
@@ -1347,15 +1373,15 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>66</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D5" t="e">
         <v>#N/A</v>
@@ -1379,141 +1405,141 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" t="s">
         <v>29</v>
       </c>
-      <c r="L5" t="s">
-        <v>30</v>
-      </c>
       <c r="M5" t="s">
-        <v>55</v>
-      </c>
-      <c r="N5">
+        <v>54</v>
+      </c>
+      <c r="N5" s="3">
         <v>300</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>30</v>
-      </c>
-      <c r="R5">
-        <v>0.25</v>
+        <v>0</v>
+      </c>
+      <c r="P5" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>30</v>
+      </c>
+      <c r="R5" s="3">
+        <v>1</v>
       </c>
       <c r="S5" t="b">
         <v>0</v>
       </c>
-      <c r="T5">
-        <v>0.8</v>
-      </c>
-      <c r="U5">
+      <c r="T5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U5" s="3">
         <v>0.5</v>
       </c>
       <c r="V5" t="b">
         <v>0</v>
       </c>
-      <c r="W5">
-        <v>0.8</v>
-      </c>
-      <c r="X5">
-        <v>50</v>
-      </c>
-      <c r="Y5">
-        <v>50</v>
-      </c>
-      <c r="Z5">
+      <c r="W5" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X5" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y5" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z5" s="3">
         <v>2</v>
       </c>
-      <c r="AA5">
-        <v>3</v>
-      </c>
-      <c r="AB5">
-        <v>10</v>
-      </c>
-      <c r="AC5">
-        <v>50</v>
-      </c>
-      <c r="AD5">
+      <c r="AA5" s="3">
+        <v>5</v>
+      </c>
+      <c r="AB5" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC5" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD5" s="3">
         <v>82</v>
       </c>
-      <c r="AE5">
-        <v>300</v>
-      </c>
-      <c r="AF5">
+      <c r="AE5" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF5" s="3">
         <v>30</v>
       </c>
       <c r="AG5" t="b">
         <v>1</v>
       </c>
-      <c r="AH5">
+      <c r="AH5" s="3">
         <v>20</v>
       </c>
-      <c r="AI5">
-        <v>3</v>
-      </c>
-      <c r="AJ5">
+      <c r="AI5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AJ5" s="3">
         <v>0.8</v>
       </c>
       <c r="AK5" t="b">
         <v>0</v>
       </c>
-      <c r="AL5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV5" t="e">
-        <v>#N/A</v>
+      <c r="AL5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN5" s="5">
+        <v>30</v>
+      </c>
+      <c r="AO5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="AQ5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="AT5" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU5" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="AV5" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="AW5" t="e">
+        <f>#N/A</f>
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>68</v>
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>69</v>
-      </c>
-      <c r="E6" t="str">
-        <f t="shared" ref="E6:E25" si="4">PROPER(TRUE)</f>
-        <v>True</v>
-      </c>
-      <c r="F6" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
         <v>10</v>
       </c>
       <c r="G6" t="s">
@@ -1522,1722 +1548,1635 @@
       <c r="H6" s="2">
         <v>8</v>
       </c>
-      <c r="I6" t="str">
-        <f t="shared" ref="I6:J21" si="5">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="J6" t="str">
-        <f t="shared" ref="J6:J17" si="6">PROPER(TRUE)</f>
-        <v>True</v>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
       </c>
       <c r="K6" t="s">
+        <v>28</v>
+      </c>
+      <c r="L6" t="s">
         <v>29</v>
       </c>
-      <c r="L6" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6" s="3">
-        <v>300</v>
-      </c>
-      <c r="O6" t="str">
-        <f t="shared" ref="O6:O17" si="7">PROPER(TRUE)</f>
-        <v>True</v>
-      </c>
-      <c r="P6" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="3">
-        <v>30</v>
-      </c>
-      <c r="R6" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="S6" t="str">
-        <f t="shared" ref="S6:S25" si="8">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="T6" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U6" s="3">
+        <v>54</v>
+      </c>
+      <c r="N6">
+        <v>300</v>
+      </c>
+      <c r="O6" t="b">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>30</v>
+      </c>
+      <c r="R6">
         <v>0.5</v>
       </c>
-      <c r="V6" t="str">
-        <f t="shared" ref="V6:V25" si="9">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="W6" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X6" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y6" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z6" s="5">
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0.8</v>
+      </c>
+      <c r="U6">
+        <v>0.5</v>
+      </c>
+      <c r="V6" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.8</v>
+      </c>
+      <c r="X6">
+        <v>50</v>
+      </c>
+      <c r="Y6">
+        <v>50</v>
+      </c>
+      <c r="Z6">
         <v>2</v>
       </c>
-      <c r="AA6" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB6" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC6" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD6" s="3">
+      <c r="AA6">
+        <v>3</v>
+      </c>
+      <c r="AB6">
+        <v>10</v>
+      </c>
+      <c r="AC6">
+        <v>50</v>
+      </c>
+      <c r="AD6">
         <v>82</v>
       </c>
-      <c r="AE6" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF6" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG6" t="str">
-        <f t="shared" ref="AG6:AG17" si="10">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="AH6" s="3">
+      <c r="AE6">
+        <v>300</v>
+      </c>
+      <c r="AF6">
+        <v>30</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6">
         <v>20</v>
       </c>
-      <c r="AI6" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ6" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK6" t="str">
-        <f t="shared" ref="AK6:AK25" si="11">PROPER(FALSE)</f>
-        <v>False</v>
-      </c>
-      <c r="AL6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV6" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW6" s="5" t="e">
+      <c r="AI6">
+        <v>3</v>
+      </c>
+      <c r="AJ6">
+        <v>0.8</v>
+      </c>
+      <c r="AK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV6" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW6" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>68</v>
+        <v>64</v>
+      </c>
+      <c r="B7" t="s">
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F7" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
         <v>10</v>
       </c>
       <c r="G7" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="2">
         <v>8</v>
       </c>
-      <c r="I7" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J7" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
+      <c r="I7" t="b">
+        <v>0</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
       </c>
       <c r="K7" t="s">
+        <v>28</v>
+      </c>
+      <c r="L7" t="s">
         <v>29</v>
       </c>
-      <c r="L7" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M7" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="3">
-        <v>300</v>
-      </c>
-      <c r="O7" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P7" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="3">
-        <v>30</v>
-      </c>
-      <c r="R7" s="3">
-        <v>1</v>
-      </c>
-      <c r="S7" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T7" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U7" s="3">
+        <v>54</v>
+      </c>
+      <c r="N7">
+        <v>300</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>30</v>
+      </c>
+      <c r="R7">
+        <v>0.25</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0.8</v>
+      </c>
+      <c r="U7">
         <v>0.5</v>
       </c>
-      <c r="V7" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W7" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X7" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y7" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z7" s="5">
+      <c r="V7" t="b">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.8</v>
+      </c>
+      <c r="X7">
+        <v>50</v>
+      </c>
+      <c r="Y7">
+        <v>50</v>
+      </c>
+      <c r="Z7">
         <v>2</v>
       </c>
-      <c r="AA7" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB7" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC7" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD7" s="3">
+      <c r="AA7">
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <v>10</v>
+      </c>
+      <c r="AC7">
+        <v>50</v>
+      </c>
+      <c r="AD7">
         <v>82</v>
       </c>
-      <c r="AE7" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF7" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG7" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH7" s="3">
+      <c r="AE7">
+        <v>300</v>
+      </c>
+      <c r="AF7">
+        <v>30</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH7">
         <v>20</v>
       </c>
-      <c r="AI7" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ7" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK7" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV7" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW7" s="5" t="e">
+      <c r="AI7">
+        <v>3</v>
+      </c>
+      <c r="AJ7">
+        <v>0.8</v>
+      </c>
+      <c r="AK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV7" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW7" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>68</v>
+        <v>99</v>
+      </c>
+      <c r="B8" t="s">
+        <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F8" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
         <v>10</v>
       </c>
       <c r="G8" t="s">
         <v>9</v>
       </c>
-      <c r="H8" s="2">
-        <v>6</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J8" t="str">
-        <f t="shared" si="6"/>
-        <v>True</v>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
       </c>
       <c r="K8" t="s">
+        <v>28</v>
+      </c>
+      <c r="L8" t="s">
         <v>29</v>
       </c>
-      <c r="L8" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M8" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="3">
-        <v>300</v>
-      </c>
-      <c r="O8" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P8" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>30</v>
-      </c>
-      <c r="R8" s="3">
-        <v>1.25</v>
-      </c>
-      <c r="S8" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U8" s="3">
+        <v>54</v>
+      </c>
+      <c r="N8">
+        <v>300</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>30</v>
+      </c>
+      <c r="R8">
+        <v>1.75</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0.8</v>
+      </c>
+      <c r="U8">
         <v>0.5</v>
       </c>
-      <c r="V8" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W8" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X8" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y8" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z8" s="5">
+      <c r="V8" t="b">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.8</v>
+      </c>
+      <c r="X8">
+        <v>50</v>
+      </c>
+      <c r="Y8">
+        <v>50</v>
+      </c>
+      <c r="Z8">
         <v>2</v>
       </c>
-      <c r="AA8" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB8" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC8" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD8" s="3">
+      <c r="AA8">
+        <v>3</v>
+      </c>
+      <c r="AB8">
+        <v>10</v>
+      </c>
+      <c r="AC8">
+        <v>50</v>
+      </c>
+      <c r="AD8">
         <v>82</v>
       </c>
-      <c r="AE8" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF8" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG8" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH8" s="3">
+      <c r="AE8">
+        <v>300</v>
+      </c>
+      <c r="AF8">
+        <v>30</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH8">
         <v>20</v>
       </c>
-      <c r="AI8" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ8" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK8" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV8" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW8" s="5" t="e">
+      <c r="AI8">
+        <v>3</v>
+      </c>
+      <c r="AJ8">
+        <v>0.8</v>
+      </c>
+      <c r="AK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV8" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW8" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>68</v>
+        <v>100</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>69</v>
-      </c>
-      <c r="E9" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F9" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
       <c r="G9" t="s">
         <v>9</v>
       </c>
-      <c r="H9" s="2">
-        <v>8</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J9" t="str">
-        <f t="shared" si="6"/>
-        <v>True</v>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
       </c>
       <c r="K9" t="s">
+        <v>28</v>
+      </c>
+      <c r="L9" t="s">
         <v>29</v>
       </c>
-      <c r="L9" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" s="3">
-        <v>300</v>
-      </c>
-      <c r="O9" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P9" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>30</v>
-      </c>
-      <c r="R9" s="3">
-        <v>1</v>
-      </c>
-      <c r="S9" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U9" s="3">
+        <v>54</v>
+      </c>
+      <c r="N9">
+        <v>300</v>
+      </c>
+      <c r="O9" t="b">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>30</v>
+      </c>
+      <c r="R9">
+        <v>1.75</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9">
+        <v>0.8</v>
+      </c>
+      <c r="U9">
         <v>0.5</v>
       </c>
-      <c r="V9" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W9" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X9" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y9" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z9" s="5">
+      <c r="V9" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.8</v>
+      </c>
+      <c r="X9">
+        <v>50</v>
+      </c>
+      <c r="Y9">
+        <v>50</v>
+      </c>
+      <c r="Z9">
         <v>2</v>
       </c>
-      <c r="AA9" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB9" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC9" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD9" s="3">
+      <c r="AA9">
+        <v>3</v>
+      </c>
+      <c r="AB9">
+        <v>10</v>
+      </c>
+      <c r="AC9">
+        <v>50</v>
+      </c>
+      <c r="AD9">
         <v>82</v>
       </c>
-      <c r="AE9" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF9" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG9" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH9" s="3">
+      <c r="AE9">
+        <v>300</v>
+      </c>
+      <c r="AF9">
+        <v>30</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH9">
         <v>20</v>
       </c>
-      <c r="AI9" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ9" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK9" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV9" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW9" s="5" t="e">
+      <c r="AI9">
+        <v>3</v>
+      </c>
+      <c r="AJ9">
+        <v>0.8</v>
+      </c>
+      <c r="AK9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV9" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW9" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>68</v>
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E10" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F10" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" t="s">
         <v>10</v>
       </c>
       <c r="G10" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="2">
-        <v>8</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J10" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
       </c>
       <c r="K10" t="s">
+        <v>28</v>
+      </c>
+      <c r="L10" t="s">
         <v>29</v>
       </c>
-      <c r="L10" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="3">
-        <v>300</v>
-      </c>
-      <c r="O10" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P10" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>30</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="S10" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T10" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U10" s="3">
+        <v>54</v>
+      </c>
+      <c r="N10">
+        <v>300</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+      <c r="P10">
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <v>30</v>
+      </c>
+      <c r="R10">
+        <v>1.75</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10">
+        <v>0.8</v>
+      </c>
+      <c r="U10">
         <v>0.5</v>
       </c>
-      <c r="V10" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X10" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z10" s="5">
+      <c r="V10" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.8</v>
+      </c>
+      <c r="X10">
+        <v>50</v>
+      </c>
+      <c r="Y10">
+        <v>50</v>
+      </c>
+      <c r="Z10">
         <v>2</v>
       </c>
-      <c r="AA10" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD10" s="3">
+      <c r="AA10">
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <v>10</v>
+      </c>
+      <c r="AC10">
+        <v>50</v>
+      </c>
+      <c r="AD10">
         <v>82</v>
       </c>
-      <c r="AE10" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG10" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH10" s="3">
+      <c r="AE10">
+        <v>300</v>
+      </c>
+      <c r="AF10">
+        <v>30</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH10">
         <v>20</v>
       </c>
-      <c r="AI10" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK10" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV10" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW10" s="5" t="e">
+      <c r="AI10">
+        <v>3</v>
+      </c>
+      <c r="AJ10">
+        <v>0.8</v>
+      </c>
+      <c r="AK10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV10" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW10" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>68</v>
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F11" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="D11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
         <v>10</v>
       </c>
       <c r="G11" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="2">
-        <v>8</v>
-      </c>
-      <c r="I11" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J11" t="str">
-        <f t="shared" si="6"/>
-        <v>True</v>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="b">
+        <v>0</v>
       </c>
       <c r="K11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L11" t="s">
         <v>29</v>
       </c>
-      <c r="L11" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M11" t="s">
-        <v>55</v>
-      </c>
-      <c r="N11" s="3">
-        <v>300</v>
-      </c>
-      <c r="O11" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P11" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>30</v>
-      </c>
-      <c r="R11" s="3">
-        <v>1</v>
-      </c>
-      <c r="S11" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T11" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U11" s="3">
+        <v>54</v>
+      </c>
+      <c r="N11">
+        <v>300</v>
+      </c>
+      <c r="O11" t="b">
+        <v>1</v>
+      </c>
+      <c r="P11">
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <v>30</v>
+      </c>
+      <c r="R11">
+        <v>1.75</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0.8</v>
+      </c>
+      <c r="U11">
         <v>0.5</v>
       </c>
-      <c r="V11" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W11" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X11" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y11" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z11" s="5">
+      <c r="V11" t="b">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.8</v>
+      </c>
+      <c r="X11">
+        <v>50</v>
+      </c>
+      <c r="Y11">
+        <v>50</v>
+      </c>
+      <c r="Z11">
         <v>2</v>
       </c>
-      <c r="AA11" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB11" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC11" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD11" s="3">
+      <c r="AA11">
+        <v>3</v>
+      </c>
+      <c r="AB11">
+        <v>10</v>
+      </c>
+      <c r="AC11">
+        <v>50</v>
+      </c>
+      <c r="AD11">
         <v>82</v>
       </c>
-      <c r="AE11" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF11" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG11" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH11" s="3">
+      <c r="AE11">
+        <v>300</v>
+      </c>
+      <c r="AF11">
+        <v>30</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH11">
         <v>20</v>
       </c>
-      <c r="AI11" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ11" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK11" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV11" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW11" s="5" t="e">
+      <c r="AI11">
+        <v>3</v>
+      </c>
+      <c r="AJ11">
+        <v>0.8</v>
+      </c>
+      <c r="AK11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV11" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW11" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>68</v>
+        <v>103</v>
+      </c>
+      <c r="B12" t="s">
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D12" t="s">
-        <v>72</v>
-      </c>
-      <c r="E12" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F12" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
         <v>10</v>
       </c>
       <c r="G12" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="2">
-        <v>8</v>
-      </c>
-      <c r="I12" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J12" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
       </c>
       <c r="K12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L12" t="s">
         <v>29</v>
       </c>
-      <c r="L12" t="s">
-        <v>30</v>
-      </c>
       <c r="M12" t="s">
-        <v>55</v>
-      </c>
-      <c r="N12" s="3">
-        <v>300</v>
-      </c>
-      <c r="O12" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P12" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>30</v>
-      </c>
-      <c r="R12" s="3">
+        <v>54</v>
+      </c>
+      <c r="N12">
+        <v>300</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>30</v>
+      </c>
+      <c r="R12">
+        <v>1.75</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0.8</v>
+      </c>
+      <c r="U12">
         <v>0.5</v>
       </c>
-      <c r="S12" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T12" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="V12" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W12" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X12" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y12" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z12" s="5">
-        <v>2</v>
-      </c>
-      <c r="AA12" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB12" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC12" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD12" s="3">
+      <c r="V12" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.8</v>
+      </c>
+      <c r="X12">
+        <v>50</v>
+      </c>
+      <c r="Y12">
+        <v>50</v>
+      </c>
+      <c r="Z12">
+        <v>10</v>
+      </c>
+      <c r="AA12">
+        <v>3</v>
+      </c>
+      <c r="AB12">
+        <v>10</v>
+      </c>
+      <c r="AC12">
+        <v>50</v>
+      </c>
+      <c r="AD12">
         <v>82</v>
       </c>
-      <c r="AE12" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF12" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG12" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH12" s="3">
+      <c r="AE12">
+        <v>300</v>
+      </c>
+      <c r="AF12">
+        <v>30</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH12">
         <v>20</v>
       </c>
-      <c r="AI12" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ12" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK12" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV12" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW12" s="5" t="e">
+      <c r="AI12">
+        <v>3</v>
+      </c>
+      <c r="AJ12">
+        <v>0.8</v>
+      </c>
+      <c r="AK12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV12" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW12" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>68</v>
+        <v>104</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>69</v>
-      </c>
-      <c r="E13" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F13" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
         <v>10</v>
       </c>
       <c r="G13" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="I13" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J13" t="str">
-        <f t="shared" si="6"/>
-        <v>True</v>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
       </c>
       <c r="K13" t="s">
+        <v>28</v>
+      </c>
+      <c r="L13" t="s">
         <v>29</v>
       </c>
-      <c r="L13" t="s">
-        <v>30</v>
-      </c>
       <c r="M13" t="s">
-        <v>55</v>
-      </c>
-      <c r="N13" s="3">
-        <v>300</v>
-      </c>
-      <c r="O13" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P13" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>30</v>
-      </c>
-      <c r="R13" s="3">
-        <v>1</v>
-      </c>
-      <c r="S13" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T13" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U13" s="3">
+        <v>54</v>
+      </c>
+      <c r="N13">
+        <v>300</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <v>30</v>
+      </c>
+      <c r="R13">
+        <v>1.75</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0.8</v>
+      </c>
+      <c r="U13">
         <v>0.5</v>
       </c>
-      <c r="V13" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W13" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X13" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y13" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z13" s="5">
-        <v>2</v>
-      </c>
-      <c r="AA13" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB13" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC13" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD13" s="3">
+      <c r="V13" t="b">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.8</v>
+      </c>
+      <c r="X13">
+        <v>50</v>
+      </c>
+      <c r="Y13">
+        <v>50</v>
+      </c>
+      <c r="Z13">
+        <v>10</v>
+      </c>
+      <c r="AA13">
+        <v>3</v>
+      </c>
+      <c r="AB13">
+        <v>10</v>
+      </c>
+      <c r="AC13">
+        <v>50</v>
+      </c>
+      <c r="AD13">
         <v>82</v>
       </c>
-      <c r="AE13" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF13" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG13" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH13" s="3">
+      <c r="AE13">
+        <v>300</v>
+      </c>
+      <c r="AF13">
+        <v>30</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH13">
         <v>20</v>
       </c>
-      <c r="AI13" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ13" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK13" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV13" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW13" s="5" t="e">
+      <c r="AI13">
+        <v>3</v>
+      </c>
+      <c r="AJ13">
+        <v>0.8</v>
+      </c>
+      <c r="AK13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV13" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW13" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>68</v>
+        <v>105</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F14" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
         <v>10</v>
       </c>
       <c r="G14" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="2">
-        <v>8</v>
-      </c>
-      <c r="I14" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J14" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
       </c>
       <c r="K14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L14" t="s">
         <v>29</v>
       </c>
-      <c r="L14" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M14" t="s">
-        <v>55</v>
-      </c>
-      <c r="N14" s="3">
-        <v>300</v>
-      </c>
-      <c r="O14" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P14" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>30</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1</v>
-      </c>
-      <c r="S14" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U14" s="3">
+        <v>54</v>
+      </c>
+      <c r="N14">
+        <v>300</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14">
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <v>30</v>
+      </c>
+      <c r="R14">
+        <v>1.75</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <v>0.8</v>
+      </c>
+      <c r="U14">
         <v>0.5</v>
       </c>
-      <c r="V14" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X14" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y14" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z14" s="5">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB14" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC14" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD14" s="3">
+      <c r="V14" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.8</v>
+      </c>
+      <c r="X14">
+        <v>50</v>
+      </c>
+      <c r="Y14">
+        <v>50</v>
+      </c>
+      <c r="Z14">
+        <v>10</v>
+      </c>
+      <c r="AA14">
+        <v>3</v>
+      </c>
+      <c r="AB14">
+        <v>10</v>
+      </c>
+      <c r="AC14">
+        <v>50</v>
+      </c>
+      <c r="AD14">
         <v>82</v>
       </c>
-      <c r="AE14" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF14" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG14" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH14" s="3">
+      <c r="AE14">
+        <v>300</v>
+      </c>
+      <c r="AF14">
+        <v>30</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH14">
         <v>20</v>
       </c>
-      <c r="AI14" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ14" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK14" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV14" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW14" s="5" t="e">
+      <c r="AI14">
+        <v>3</v>
+      </c>
+      <c r="AJ14">
+        <v>0.8</v>
+      </c>
+      <c r="AK14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV14" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW14" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>68</v>
+        <v>106</v>
+      </c>
+      <c r="B15" t="s">
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
-      </c>
-      <c r="D15" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F15" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" t="s">
         <v>10</v>
       </c>
       <c r="G15" t="s">
         <v>9</v>
       </c>
-      <c r="H15" s="2">
-        <v>8</v>
-      </c>
-      <c r="I15" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J15" t="str">
-        <f t="shared" si="6"/>
-        <v>True</v>
+      <c r="H15">
+        <v>2</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="b">
+        <v>0</v>
       </c>
       <c r="K15" t="s">
+        <v>28</v>
+      </c>
+      <c r="L15" t="s">
         <v>29</v>
       </c>
-      <c r="L15" t="s">
-        <v>30</v>
-      </c>
       <c r="M15" t="s">
-        <v>55</v>
-      </c>
-      <c r="N15" s="3">
-        <v>300</v>
-      </c>
-      <c r="O15" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P15" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>30</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0.75</v>
-      </c>
-      <c r="S15" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U15" s="3">
+        <v>54</v>
+      </c>
+      <c r="N15">
+        <v>300</v>
+      </c>
+      <c r="O15" t="b">
+        <v>1</v>
+      </c>
+      <c r="P15">
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <v>30</v>
+      </c>
+      <c r="R15">
+        <v>1.75</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15">
+        <v>0.8</v>
+      </c>
+      <c r="U15">
         <v>0.5</v>
       </c>
-      <c r="V15" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W15" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X15" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z15" s="5">
-        <v>2</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB15" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD15" s="3">
+      <c r="V15" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.8</v>
+      </c>
+      <c r="X15">
+        <v>50</v>
+      </c>
+      <c r="Y15">
+        <v>50</v>
+      </c>
+      <c r="Z15">
+        <v>10</v>
+      </c>
+      <c r="AA15">
+        <v>3</v>
+      </c>
+      <c r="AB15">
+        <v>10</v>
+      </c>
+      <c r="AC15">
+        <v>50</v>
+      </c>
+      <c r="AD15">
         <v>82</v>
       </c>
-      <c r="AE15" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG15" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH15" s="3">
+      <c r="AE15">
+        <v>300</v>
+      </c>
+      <c r="AF15">
+        <v>30</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH15">
         <v>20</v>
       </c>
-      <c r="AI15" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ15" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK15" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV15" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW15" s="5" t="e">
+      <c r="AI15">
+        <v>3</v>
+      </c>
+      <c r="AJ15">
+        <v>0.8</v>
+      </c>
+      <c r="AK15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV15" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW15" t="e">
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>68</v>
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="D16" t="s">
-        <v>82</v>
-      </c>
-      <c r="E16" t="str">
-        <f t="shared" si="4"/>
-        <v>True</v>
-      </c>
-      <c r="F16" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
+      </c>
+      <c r="F16" t="s">
         <v>10</v>
       </c>
       <c r="G16" t="s">
         <v>9</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16">
         <v>2</v>
       </c>
-      <c r="I16" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
-      </c>
-      <c r="J16" t="str">
-        <f t="shared" si="6"/>
-        <v>True</v>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
       </c>
       <c r="K16" t="s">
+        <v>28</v>
+      </c>
+      <c r="L16" t="s">
         <v>29</v>
       </c>
-      <c r="L16" t="s">
-        <v>30</v>
-      </c>
       <c r="M16" t="s">
-        <v>55</v>
-      </c>
-      <c r="N16" s="3">
-        <v>300</v>
-      </c>
-      <c r="O16" t="str">
-        <f t="shared" si="7"/>
-        <v>True</v>
-      </c>
-      <c r="P16" s="3">
-        <v>1</v>
-      </c>
-      <c r="Q16" s="3">
-        <v>30</v>
-      </c>
-      <c r="R16" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="S16" t="str">
-        <f t="shared" si="8"/>
-        <v>False</v>
-      </c>
-      <c r="T16" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="U16" s="3">
+        <v>54</v>
+      </c>
+      <c r="N16">
+        <v>300</v>
+      </c>
+      <c r="O16" t="b">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <v>30</v>
+      </c>
+      <c r="R16">
+        <v>1.75</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0.8</v>
+      </c>
+      <c r="U16">
         <v>0.5</v>
       </c>
-      <c r="V16" t="str">
-        <f t="shared" si="9"/>
-        <v>False</v>
-      </c>
-      <c r="W16" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="X16" s="3">
-        <v>50</v>
-      </c>
-      <c r="Y16" s="3">
-        <v>50</v>
-      </c>
-      <c r="Z16" s="5">
-        <v>2</v>
-      </c>
-      <c r="AA16" s="3">
-        <v>3</v>
-      </c>
-      <c r="AB16" s="3">
-        <v>10</v>
-      </c>
-      <c r="AC16" s="3">
-        <v>50</v>
-      </c>
-      <c r="AD16" s="3">
+      <c r="V16" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.8</v>
+      </c>
+      <c r="X16">
+        <v>50</v>
+      </c>
+      <c r="Y16">
+        <v>50</v>
+      </c>
+      <c r="Z16">
+        <v>10</v>
+      </c>
+      <c r="AA16">
+        <v>3</v>
+      </c>
+      <c r="AB16">
+        <v>10</v>
+      </c>
+      <c r="AC16">
+        <v>50</v>
+      </c>
+      <c r="AD16">
         <v>82</v>
       </c>
-      <c r="AE16" s="3">
-        <v>300</v>
-      </c>
-      <c r="AF16" s="3">
-        <v>30</v>
-      </c>
-      <c r="AG16" t="str">
-        <f t="shared" si="10"/>
-        <v>False</v>
-      </c>
-      <c r="AH16" s="3">
+      <c r="AE16">
+        <v>300</v>
+      </c>
+      <c r="AF16">
+        <v>30</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH16">
         <v>20</v>
       </c>
-      <c r="AI16" s="3">
-        <v>3</v>
-      </c>
-      <c r="AJ16" s="3">
-        <v>0.8</v>
-      </c>
-      <c r="AK16" t="str">
-        <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV16" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW16" s="5" t="e">
+      <c r="AI16">
+        <v>3</v>
+      </c>
+      <c r="AJ16">
+        <v>0.8</v>
+      </c>
+      <c r="AK16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV16" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW16" t="e">
         <v>#N/A</v>
       </c>
     </row>
     <row r="17" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="E17:E36" si="0">PROPER(TRUE)</f>
         <v>True</v>
       </c>
       <c r="F17" s="5" t="s">
@@ -3250,27 +3189,27 @@
         <v>8</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="I17:J32" si="1">PROPER(FALSE)</f>
         <v>False</v>
       </c>
       <c r="J17" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="J17:J28" si="2">PROPER(TRUE)</f>
         <v>True</v>
       </c>
       <c r="K17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L17" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="M17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N17" s="3">
         <v>300</v>
       </c>
       <c r="O17" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="O17:O28" si="3">PROPER(TRUE)</f>
         <v>True</v>
       </c>
       <c r="P17" s="3">
@@ -3283,7 +3222,7 @@
         <v>0.75</v>
       </c>
       <c r="S17" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="S17:S36" si="4">PROPER(FALSE)</f>
         <v>False</v>
       </c>
       <c r="T17" s="3">
@@ -3293,7 +3232,7 @@
         <v>0.5</v>
       </c>
       <c r="V17" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="V17:V36" si="5">PROPER(FALSE)</f>
         <v>False</v>
       </c>
       <c r="W17" s="3">
@@ -3327,7 +3266,7 @@
         <v>30</v>
       </c>
       <c r="AG17" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="AG17:AG28" si="6">PROPER(FALSE)</f>
         <v>False</v>
       </c>
       <c r="AH17" s="3">
@@ -3340,7 +3279,7 @@
         <v>0.8</v>
       </c>
       <c r="AK17" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="AK17:AK36" si="7">PROPER(FALSE)</f>
         <v>False</v>
       </c>
       <c r="AL17" s="5" t="e">
@@ -3382,21 +3321,20 @@
     </row>
     <row r="18" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B18" t="s">
-        <v>44</v>
+        <v>69</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C18" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" t="e">
-        <f>#N/A</f>
-        <v>#N/A</v>
+        <v>35</v>
+      </c>
+      <c r="D18" t="s">
+        <v>70</v>
       </c>
       <c r="E18" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
+        <f t="shared" si="0"/>
+        <v>True</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>10</v>
@@ -3404,32 +3342,32 @@
       <c r="G18" t="s">
         <v>9</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="6">
         <v>8</v>
       </c>
       <c r="I18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="K18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L18" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="M18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N18" s="3">
         <v>300</v>
       </c>
       <c r="O18" t="str">
-        <f t="shared" ref="O18:O20" si="12">PROPER(FALSE)</f>
-        <v>False</v>
+        <f t="shared" si="3"/>
+        <v>True</v>
       </c>
       <c r="P18" s="3">
         <v>1</v>
@@ -3438,10 +3376,10 @@
         <v>30</v>
       </c>
       <c r="R18" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S18" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T18" s="3">
@@ -3451,7 +3389,7 @@
         <v>0.5</v>
       </c>
       <c r="V18" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W18" s="3">
@@ -3485,8 +3423,8 @@
         <v>30</v>
       </c>
       <c r="AG18" t="str">
-        <f t="shared" ref="AG18:AG20" si="13">PROPER(TRUE)</f>
-        <v>True</v>
+        <f t="shared" si="6"/>
+        <v>False</v>
       </c>
       <c r="AH18" s="3">
         <v>20</v>
@@ -3498,7 +3436,7 @@
         <v>0.8</v>
       </c>
       <c r="AK18" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL18" s="5" t="e">
@@ -3540,21 +3478,20 @@
     </row>
     <row r="19" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B19" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" t="s">
         <v>44</v>
       </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="e">
-        <f>#N/A</f>
-        <v>#N/A</v>
+      <c r="D19" t="s">
+        <v>67</v>
       </c>
       <c r="E19" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
+        <f t="shared" si="0"/>
+        <v>True</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>10</v>
@@ -3563,31 +3500,31 @@
         <v>9</v>
       </c>
       <c r="H19" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J19" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
+        <f t="shared" si="2"/>
+        <v>True</v>
       </c>
       <c r="K19" t="s">
-        <v>86</v>
-      </c>
-      <c r="L19" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="M19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N19" s="3">
         <v>300</v>
       </c>
       <c r="O19" t="str">
-        <f t="shared" si="12"/>
-        <v>False</v>
+        <f t="shared" si="3"/>
+        <v>True</v>
       </c>
       <c r="P19" s="3">
         <v>1</v>
@@ -3596,10 +3533,10 @@
         <v>30</v>
       </c>
       <c r="R19" s="3">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T19" s="3">
@@ -3609,7 +3546,7 @@
         <v>0.5</v>
       </c>
       <c r="V19" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W19" s="3">
@@ -3643,8 +3580,8 @@
         <v>30</v>
       </c>
       <c r="AG19" t="str">
-        <f t="shared" si="13"/>
-        <v>True</v>
+        <f t="shared" si="6"/>
+        <v>False</v>
       </c>
       <c r="AH19" s="3">
         <v>20</v>
@@ -3656,7 +3593,7 @@
         <v>0.8</v>
       </c>
       <c r="AK19" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL19" s="5" t="e">
@@ -3698,21 +3635,20 @@
     </row>
     <row r="20" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" t="s">
-        <v>44</v>
+        <v>72</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="e">
-        <f>#N/A</f>
-        <v>#N/A</v>
+        <v>35</v>
+      </c>
+      <c r="D20" t="s">
+        <v>67</v>
       </c>
       <c r="E20" t="str">
-        <f>PROPER(FALSE)</f>
-        <v>False</v>
+        <f t="shared" si="0"/>
+        <v>True</v>
       </c>
       <c r="F20" s="5" t="s">
         <v>10</v>
@@ -3724,28 +3660,28 @@
         <v>8</v>
       </c>
       <c r="I20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J20" t="str">
-        <f t="shared" si="5"/>
-        <v>False</v>
+        <f t="shared" si="2"/>
+        <v>True</v>
       </c>
       <c r="K20" t="s">
-        <v>86</v>
-      </c>
-      <c r="L20" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="M20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N20" s="3">
         <v>300</v>
       </c>
       <c r="O20" t="str">
-        <f t="shared" si="12"/>
-        <v>False</v>
+        <f t="shared" si="3"/>
+        <v>True</v>
       </c>
       <c r="P20" s="3">
         <v>1</v>
@@ -3754,10 +3690,10 @@
         <v>30</v>
       </c>
       <c r="R20" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S20" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T20" s="3">
@@ -3767,7 +3703,7 @@
         <v>0.5</v>
       </c>
       <c r="V20" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W20" s="3">
@@ -3801,8 +3737,8 @@
         <v>30</v>
       </c>
       <c r="AG20" t="str">
-        <f t="shared" si="13"/>
-        <v>True</v>
+        <f t="shared" si="6"/>
+        <v>False</v>
       </c>
       <c r="AH20" s="3">
         <v>20</v>
@@ -3814,7 +3750,7 @@
         <v>0.8</v>
       </c>
       <c r="AK20" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL20" s="5" t="e">
@@ -3854,21 +3790,21 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>True</v>
       </c>
       <c r="F21" s="5" t="s">
@@ -3878,32 +3814,32 @@
         <v>9</v>
       </c>
       <c r="H21" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J21" t="str">
-        <f t="shared" ref="J21:J25" si="14">PROPER(TRUE)</f>
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K21" t="s">
+        <v>28</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N21" s="3">
+        <v>300</v>
+      </c>
+      <c r="O21" t="str">
+        <f t="shared" si="3"/>
         <v>True</v>
       </c>
-      <c r="K21" t="s">
-        <v>29</v>
-      </c>
-      <c r="L21" t="s">
-        <v>30</v>
-      </c>
-      <c r="M21" t="s">
-        <v>55</v>
-      </c>
-      <c r="N21" s="3">
-        <v>300</v>
-      </c>
-      <c r="O21" t="str">
-        <f t="shared" ref="O21:O25" si="15">PROPER(TRUE)</f>
-        <v>True</v>
-      </c>
       <c r="P21" s="3">
         <v>1</v>
       </c>
@@ -3911,10 +3847,10 @@
         <v>30</v>
       </c>
       <c r="R21" s="3">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="S21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T21" s="3">
@@ -3924,7 +3860,7 @@
         <v>0.5</v>
       </c>
       <c r="V21" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W21" s="3">
@@ -3958,7 +3894,7 @@
         <v>30</v>
       </c>
       <c r="AG21" t="str">
-        <f t="shared" ref="AG21:AG25" si="16">PROPER(FALSE)</f>
+        <f t="shared" si="6"/>
         <v>False</v>
       </c>
       <c r="AH21" s="3">
@@ -3971,7 +3907,7 @@
         <v>0.8</v>
       </c>
       <c r="AK21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL21" s="5" t="e">
@@ -4013,19 +3949,19 @@
     </row>
     <row r="22" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>True</v>
       </c>
       <c r="F22" s="5" t="s">
@@ -4035,30 +3971,30 @@
         <v>9</v>
       </c>
       <c r="H22" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I22" t="str">
-        <f t="shared" ref="I22:J25" si="17">PROPER(FALSE)</f>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J22" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="2"/>
         <v>True</v>
       </c>
       <c r="K22" t="s">
-        <v>29</v>
-      </c>
-      <c r="L22" t="s">
-        <v>30</v>
+        <v>28</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="M22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
       </c>
       <c r="O22" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="3"/>
         <v>True</v>
       </c>
       <c r="P22" s="3">
@@ -4068,10 +4004,10 @@
         <v>30</v>
       </c>
       <c r="R22" s="3">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="S22" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T22" s="3">
@@ -4081,7 +4017,7 @@
         <v>0.5</v>
       </c>
       <c r="V22" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W22" s="3">
@@ -4115,7 +4051,7 @@
         <v>30</v>
       </c>
       <c r="AG22" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>False</v>
       </c>
       <c r="AH22" s="3">
@@ -4128,7 +4064,7 @@
         <v>0.8</v>
       </c>
       <c r="AK22" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL22" s="5" t="e">
@@ -4170,19 +4106,19 @@
     </row>
     <row r="23" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="E23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>True</v>
       </c>
       <c r="F23" s="5" t="s">
@@ -4192,32 +4128,32 @@
         <v>9</v>
       </c>
       <c r="H23" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I23" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J23" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K23" t="s">
+        <v>28</v>
+      </c>
+      <c r="L23" t="s">
+        <v>29</v>
+      </c>
+      <c r="M23" t="s">
+        <v>54</v>
+      </c>
+      <c r="N23" s="3">
+        <v>300</v>
+      </c>
+      <c r="O23" t="str">
+        <f t="shared" si="3"/>
         <v>True</v>
       </c>
-      <c r="K23" t="s">
-        <v>29</v>
-      </c>
-      <c r="L23" t="s">
-        <v>30</v>
-      </c>
-      <c r="M23" t="s">
-        <v>55</v>
-      </c>
-      <c r="N23" s="3">
-        <v>300</v>
-      </c>
-      <c r="O23" t="str">
-        <f t="shared" si="15"/>
-        <v>True</v>
-      </c>
       <c r="P23" s="3">
         <v>1</v>
       </c>
@@ -4225,10 +4161,10 @@
         <v>30</v>
       </c>
       <c r="R23" s="3">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="S23" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T23" s="3">
@@ -4238,7 +4174,7 @@
         <v>0.5</v>
       </c>
       <c r="V23" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W23" s="3">
@@ -4272,7 +4208,7 @@
         <v>30</v>
       </c>
       <c r="AG23" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>False</v>
       </c>
       <c r="AH23" s="3">
@@ -4285,7 +4221,7 @@
         <v>0.8</v>
       </c>
       <c r="AK23" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL23" s="5" t="e">
@@ -4327,19 +4263,19 @@
     </row>
     <row r="24" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="E24" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>True</v>
       </c>
       <c r="F24" s="5" t="s">
@@ -4352,27 +4288,27 @@
         <v>2</v>
       </c>
       <c r="I24" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J24" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="2"/>
         <v>True</v>
       </c>
       <c r="K24" t="s">
+        <v>28</v>
+      </c>
+      <c r="L24" t="s">
         <v>29</v>
       </c>
-      <c r="L24" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N24" s="3">
         <v>300</v>
       </c>
       <c r="O24" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="3"/>
         <v>True</v>
       </c>
       <c r="P24" s="3">
@@ -4382,10 +4318,10 @@
         <v>30</v>
       </c>
       <c r="R24" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S24" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T24" s="3">
@@ -4395,7 +4331,7 @@
         <v>0.5</v>
       </c>
       <c r="V24" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W24" s="3">
@@ -4408,7 +4344,7 @@
         <v>50</v>
       </c>
       <c r="Z24" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA24" s="3">
         <v>3</v>
@@ -4429,7 +4365,7 @@
         <v>30</v>
       </c>
       <c r="AG24" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>False</v>
       </c>
       <c r="AH24" s="3">
@@ -4442,7 +4378,7 @@
         <v>0.8</v>
       </c>
       <c r="AK24" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="7"/>
         <v>False</v>
       </c>
       <c r="AL24" s="5" t="e">
@@ -4484,19 +4420,19 @@
     </row>
     <row r="25" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25" t="s">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="E25" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="0"/>
         <v>True</v>
       </c>
       <c r="F25" s="5" t="s">
@@ -4506,32 +4442,32 @@
         <v>9</v>
       </c>
       <c r="H25" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I25" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="1"/>
         <v>False</v>
       </c>
       <c r="J25" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K25" t="s">
+        <v>28</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M25" t="s">
+        <v>54</v>
+      </c>
+      <c r="N25" s="3">
+        <v>300</v>
+      </c>
+      <c r="O25" t="str">
+        <f t="shared" si="3"/>
         <v>True</v>
       </c>
-      <c r="K25" t="s">
-        <v>29</v>
-      </c>
-      <c r="L25" t="s">
-        <v>30</v>
-      </c>
-      <c r="M25" t="s">
-        <v>55</v>
-      </c>
-      <c r="N25" s="3">
-        <v>300</v>
-      </c>
-      <c r="O25" t="str">
-        <f t="shared" si="15"/>
-        <v>True</v>
-      </c>
       <c r="P25" s="3">
         <v>1</v>
       </c>
@@ -4539,10 +4475,10 @@
         <v>30</v>
       </c>
       <c r="R25" s="3">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S25" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="4"/>
         <v>False</v>
       </c>
       <c r="T25" s="3">
@@ -4552,7 +4488,7 @@
         <v>0.5</v>
       </c>
       <c r="V25" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="5"/>
         <v>False</v>
       </c>
       <c r="W25" s="3">
@@ -4565,7 +4501,7 @@
         <v>50</v>
       </c>
       <c r="Z25" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA25" s="3">
         <v>3</v>
@@ -4586,7 +4522,7 @@
         <v>30</v>
       </c>
       <c r="AG25" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="6"/>
         <v>False</v>
       </c>
       <c r="AH25" s="3">
@@ -4599,43 +4535,1773 @@
         <v>0.8</v>
       </c>
       <c r="AK25" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW25" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C26" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G26" t="s">
+        <v>9</v>
+      </c>
+      <c r="H26" s="2">
+        <v>8</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J26" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K26" t="s">
+        <v>28</v>
+      </c>
+      <c r="L26" t="s">
+        <v>29</v>
+      </c>
+      <c r="M26" t="s">
+        <v>54</v>
+      </c>
+      <c r="N26" s="3">
+        <v>300</v>
+      </c>
+      <c r="O26" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P26" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="3">
+        <v>30</v>
+      </c>
+      <c r="R26" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="S26" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U26" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V26" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X26" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y26" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z26" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA26" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB26" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC26" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD26" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE26" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF26" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG26" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH26" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI26" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ26" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK26" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E27" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G27" t="s">
+        <v>9</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J27" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K27" t="s">
+        <v>28</v>
+      </c>
+      <c r="L27" t="s">
+        <v>29</v>
+      </c>
+      <c r="M27" t="s">
+        <v>54</v>
+      </c>
+      <c r="N27" s="3">
+        <v>300</v>
+      </c>
+      <c r="O27" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P27" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>30</v>
+      </c>
+      <c r="R27" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S27" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U27" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V27" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X27" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y27" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z27" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA27" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB27" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC27" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD27" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE27" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF27" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG27" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH27" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI27" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ27" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK27" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW27" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" s="2">
+        <v>8</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J28" t="str">
+        <f t="shared" si="2"/>
+        <v>True</v>
+      </c>
+      <c r="K28" t="s">
+        <v>28</v>
+      </c>
+      <c r="L28" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M28" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28" s="3">
+        <v>300</v>
+      </c>
+      <c r="O28" t="str">
+        <f t="shared" si="3"/>
+        <v>True</v>
+      </c>
+      <c r="P28" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>30</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="S28" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V28" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X28" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z28" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA28" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB28" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD28" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF28" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG28" t="str">
+        <f t="shared" si="6"/>
+        <v>False</v>
+      </c>
+      <c r="AH28" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI28" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ28" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK28" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW28" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E29" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G29" t="s">
+        <v>9</v>
+      </c>
+      <c r="H29" s="2">
+        <v>8</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J29" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K29" t="s">
+        <v>28</v>
+      </c>
+      <c r="L29" t="s">
+        <v>29</v>
+      </c>
+      <c r="M29" t="s">
+        <v>54</v>
+      </c>
+      <c r="N29" s="3">
+        <v>300</v>
+      </c>
+      <c r="O29" t="str">
+        <f t="shared" ref="O29:O31" si="8">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="P29" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>30</v>
+      </c>
+      <c r="R29" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S29" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V29" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z29" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG29" t="str">
+        <f t="shared" ref="AG29:AG31" si="9">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI29" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ29" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK29" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW29" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E30" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G30" t="s">
+        <v>9</v>
+      </c>
+      <c r="H30" s="2">
+        <v>8</v>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J30" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K30" t="s">
+        <v>84</v>
+      </c>
+      <c r="L30" t="s">
+        <v>29</v>
+      </c>
+      <c r="M30" t="s">
+        <v>54</v>
+      </c>
+      <c r="N30" s="3">
+        <v>300</v>
+      </c>
+      <c r="O30" t="str">
+        <f t="shared" si="8"/>
+        <v>False</v>
+      </c>
+      <c r="P30" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>30</v>
+      </c>
+      <c r="R30" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S30" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V30" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X30" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z30" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA30" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB30" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD30" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF30" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG30" t="str">
+        <f t="shared" si="9"/>
+        <v>True</v>
+      </c>
+      <c r="AH30" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI30" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ30" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK30" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW30" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" t="e">
+        <f>#N/A</f>
+        <v>#N/A</v>
+      </c>
+      <c r="E31" t="str">
+        <f>PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G31" t="s">
+        <v>9</v>
+      </c>
+      <c r="H31" s="2">
+        <v>8</v>
+      </c>
+      <c r="I31" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J31" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="K31" t="s">
+        <v>84</v>
+      </c>
+      <c r="L31" t="s">
+        <v>29</v>
+      </c>
+      <c r="M31" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="3">
+        <v>300</v>
+      </c>
+      <c r="O31" t="str">
+        <f t="shared" si="8"/>
+        <v>False</v>
+      </c>
+      <c r="P31" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>30</v>
+      </c>
+      <c r="R31" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S31" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V31" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X31" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z31" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA31" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB31" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD31" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF31" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG31" t="str">
+        <f t="shared" si="9"/>
+        <v>True</v>
+      </c>
+      <c r="AH31" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI31" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ31" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK31" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW31" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="32" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G32" t="s">
+        <v>9</v>
+      </c>
+      <c r="H32" s="2">
+        <v>4</v>
+      </c>
+      <c r="I32" t="str">
+        <f t="shared" si="1"/>
+        <v>False</v>
+      </c>
+      <c r="J32" t="str">
+        <f t="shared" ref="J32:J36" si="10">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="K32" t="s">
+        <v>28</v>
+      </c>
+      <c r="L32" t="s">
+        <v>29</v>
+      </c>
+      <c r="M32" t="s">
+        <v>54</v>
+      </c>
+      <c r="N32" s="3">
+        <v>300</v>
+      </c>
+      <c r="O32" t="str">
+        <f t="shared" ref="O32:O36" si="11">PROPER(TRUE)</f>
+        <v>True</v>
+      </c>
+      <c r="P32" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>30</v>
+      </c>
+      <c r="R32" s="3">
+        <v>1</v>
+      </c>
+      <c r="S32" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T32" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U32" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V32" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W32" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X32" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y32" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z32" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB32" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC32" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD32" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE32" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF32" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG32" t="str">
+        <f t="shared" ref="AG32:AG36" si="12">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="AH32" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI32" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ32" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK32" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW32" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G33" t="s">
+        <v>9</v>
+      </c>
+      <c r="H33" s="2">
+        <v>2</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" ref="I33:I36" si="13">PROPER(FALSE)</f>
+        <v>False</v>
+      </c>
+      <c r="J33" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K33" t="s">
+        <v>28</v>
+      </c>
+      <c r="L33" t="s">
+        <v>29</v>
+      </c>
+      <c r="M33" t="s">
+        <v>54</v>
+      </c>
+      <c r="N33" s="3">
+        <v>300</v>
+      </c>
+      <c r="O33" t="str">
         <f t="shared" si="11"/>
-        <v>False</v>
-      </c>
-      <c r="AL25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" s="5" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25" s="5" t="e">
+        <v>True</v>
+      </c>
+      <c r="P33" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="3">
+        <v>30</v>
+      </c>
+      <c r="R33" s="3">
+        <v>1.75</v>
+      </c>
+      <c r="S33" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T33" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V33" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W33" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X33" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y33" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z33" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA33" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB33" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC33" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD33" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE33" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF33" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG33" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH33" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI33" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ33" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK33" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW33" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" t="s">
+        <v>44</v>
+      </c>
+      <c r="D34" t="s">
+        <v>88</v>
+      </c>
+      <c r="E34" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G34" t="s">
+        <v>9</v>
+      </c>
+      <c r="H34" s="2">
+        <v>2</v>
+      </c>
+      <c r="I34" t="str">
+        <f t="shared" si="13"/>
+        <v>False</v>
+      </c>
+      <c r="J34" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K34" t="s">
+        <v>28</v>
+      </c>
+      <c r="L34" t="s">
+        <v>29</v>
+      </c>
+      <c r="M34" t="s">
+        <v>54</v>
+      </c>
+      <c r="N34" s="3">
+        <v>300</v>
+      </c>
+      <c r="O34" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P34" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>30</v>
+      </c>
+      <c r="R34" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S34" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V34" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X34" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z34" s="5">
+        <v>2</v>
+      </c>
+      <c r="AA34" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB34" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD34" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF34" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG34" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH34" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI34" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ34" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK34" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW34" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" t="s">
+        <v>91</v>
+      </c>
+      <c r="D35" t="s">
+        <v>88</v>
+      </c>
+      <c r="E35" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G35" t="s">
+        <v>9</v>
+      </c>
+      <c r="H35" s="2">
+        <v>2</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="13"/>
+        <v>False</v>
+      </c>
+      <c r="J35" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K35" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="M35" t="s">
+        <v>54</v>
+      </c>
+      <c r="N35" s="3">
+        <v>300</v>
+      </c>
+      <c r="O35" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P35" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="3">
+        <v>30</v>
+      </c>
+      <c r="R35" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S35" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T35" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U35" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V35" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W35" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X35" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y35" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z35" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB35" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC35" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD35" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE35" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF35" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG35" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH35" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI35" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ35" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK35" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW35" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="36" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" t="s">
+        <v>93</v>
+      </c>
+      <c r="E36" t="str">
+        <f t="shared" si="0"/>
+        <v>True</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G36" t="s">
+        <v>9</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2</v>
+      </c>
+      <c r="I36" t="str">
+        <f t="shared" si="13"/>
+        <v>False</v>
+      </c>
+      <c r="J36" t="str">
+        <f t="shared" si="10"/>
+        <v>True</v>
+      </c>
+      <c r="K36" t="s">
+        <v>28</v>
+      </c>
+      <c r="L36" t="s">
+        <v>29</v>
+      </c>
+      <c r="M36" t="s">
+        <v>54</v>
+      </c>
+      <c r="N36" s="3">
+        <v>300</v>
+      </c>
+      <c r="O36" t="str">
+        <f t="shared" si="11"/>
+        <v>True</v>
+      </c>
+      <c r="P36" s="3">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>30</v>
+      </c>
+      <c r="R36" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="S36" t="str">
+        <f t="shared" si="4"/>
+        <v>False</v>
+      </c>
+      <c r="T36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="U36" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="V36" t="str">
+        <f t="shared" si="5"/>
+        <v>False</v>
+      </c>
+      <c r="W36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="X36" s="3">
+        <v>50</v>
+      </c>
+      <c r="Y36" s="3">
+        <v>50</v>
+      </c>
+      <c r="Z36" s="5">
+        <v>1</v>
+      </c>
+      <c r="AA36" s="3">
+        <v>3</v>
+      </c>
+      <c r="AB36" s="3">
+        <v>10</v>
+      </c>
+      <c r="AC36" s="3">
+        <v>50</v>
+      </c>
+      <c r="AD36" s="3">
+        <v>82</v>
+      </c>
+      <c r="AE36" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF36" s="3">
+        <v>30</v>
+      </c>
+      <c r="AG36" t="str">
+        <f t="shared" si="12"/>
+        <v>False</v>
+      </c>
+      <c r="AH36" s="3">
+        <v>20</v>
+      </c>
+      <c r="AI36" s="3">
+        <v>3</v>
+      </c>
+      <c r="AJ36" s="3">
+        <v>0.8</v>
+      </c>
+      <c r="AK36" t="str">
+        <f t="shared" si="7"/>
+        <v>False</v>
+      </c>
+      <c r="AL36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV36" s="5" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW36" s="5" t="e">
         <v>#N/A</v>
       </c>
     </row>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss\Documents\repos\behaviour_rig\Params\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78227AEB-11A2-46F8-804E-D68F90745DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34735BA5-584A-4AFF-A845-914C5D2D5961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="25395" windowHeight="11685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
@@ -1567,7 +1567,7 @@
         <v>300</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6">
         <v>1</v>
@@ -1829,7 +1829,7 @@
         <v>43</v>
       </c>
       <c r="C8" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="D8" t="e">
         <v>#N/A</v>
@@ -1844,7 +1844,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I8" t="b">
         <v>0</v>
@@ -1874,7 +1874,7 @@
         <v>30</v>
       </c>
       <c r="R8">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -1978,7 +1978,7 @@
         <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="D9" t="e">
         <v>#N/A</v>
@@ -1993,7 +1993,7 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I9" t="b">
         <v>0</v>
@@ -2023,7 +2023,7 @@
         <v>30</v>
       </c>
       <c r="R9">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="D10" t="e">
         <v>#N/A</v>
@@ -2142,7 +2142,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I10" t="b">
         <v>0</v>
@@ -2172,7 +2172,7 @@
         <v>30</v>
       </c>
       <c r="R10">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -2276,7 +2276,7 @@
         <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="D11" t="e">
         <v>#N/A</v>
@@ -2291,7 +2291,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I11" t="b">
         <v>0</v>
@@ -2321,7 +2321,7 @@
         <v>30</v>
       </c>
       <c r="R11">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss\Documents\repos\behaviour_rig\Params\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34735BA5-584A-4AFF-A845-914C5D2D5961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A8233-E471-4F8A-8ECF-0F0F25133A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="2940" windowWidth="25395" windowHeight="11685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Params" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1874,7 +1875,7 @@
         <v>30</v>
       </c>
       <c r="R8">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="S8" t="b">
         <v>0</v>
@@ -2023,7 +2024,7 @@
         <v>30</v>
       </c>
       <c r="R9">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="S9" t="b">
         <v>0</v>
@@ -2172,7 +2173,7 @@
         <v>30</v>
       </c>
       <c r="R10">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="b">
         <v>0</v>
@@ -2321,7 +2322,7 @@
         <v>30</v>
       </c>
       <c r="R11">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="b">
         <v>0</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss\Documents\repos\behaviour_rig\Params\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D1A8233-E471-4F8A-8ECF-0F0F25133A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24492FDE-63BC-4459-A84C-859648536AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2940" yWindow="2940" windowWidth="25395" windowHeight="11685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Params" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ss\Documents\repos\behaviour_rig\Params\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Serkan/Desktop/pro/PhD/main/repos/behaviour_rig/Params/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24492FDE-63BC-4459-A84C-859648536AD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7678C54-394D-A744-9375-F5D86B4FDE74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="25395" windowHeight="11685" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="25400" windowHeight="11680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Params" sheetId="1" r:id="rId1"/>
@@ -744,40 +744,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AW36"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.42578125" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" customWidth="1"/>
-    <col min="7" max="8" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="14.5" customWidth="1"/>
+    <col min="3" max="3" width="17.5" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="6" max="6" width="14.5" customWidth="1"/>
+    <col min="7" max="8" width="13.5" customWidth="1"/>
     <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="30.42578125" customWidth="1"/>
-    <col min="11" max="11" width="22.85546875" customWidth="1"/>
-    <col min="12" max="12" width="28.42578125" customWidth="1"/>
-    <col min="13" max="13" width="24.140625" customWidth="1"/>
-    <col min="14" max="14" width="16.42578125" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" customWidth="1"/>
+    <col min="10" max="10" width="30.5" customWidth="1"/>
+    <col min="11" max="11" width="22.83203125" customWidth="1"/>
+    <col min="12" max="12" width="28.5" customWidth="1"/>
+    <col min="13" max="13" width="24.1640625" customWidth="1"/>
+    <col min="14" max="14" width="16.5" customWidth="1"/>
+    <col min="15" max="15" width="14.5" customWidth="1"/>
     <col min="16" max="16" width="23" customWidth="1"/>
-    <col min="17" max="17" width="22.42578125" customWidth="1"/>
+    <col min="17" max="17" width="22.5" customWidth="1"/>
     <col min="18" max="22" width="23" customWidth="1"/>
-    <col min="23" max="23" width="33.42578125" customWidth="1"/>
-    <col min="24" max="35" width="24.42578125" customWidth="1"/>
-    <col min="36" max="36" width="26.42578125" customWidth="1"/>
-    <col min="37" max="38" width="15.42578125" customWidth="1"/>
-    <col min="39" max="39" width="28.42578125" customWidth="1"/>
+    <col min="23" max="23" width="33.5" customWidth="1"/>
+    <col min="24" max="35" width="24.5" customWidth="1"/>
+    <col min="36" max="36" width="26.5" customWidth="1"/>
+    <col min="37" max="38" width="15.5" customWidth="1"/>
+    <col min="39" max="39" width="28.5" customWidth="1"/>
     <col min="40" max="40" width="18" customWidth="1"/>
-    <col min="41" max="41" width="14.42578125" customWidth="1"/>
-    <col min="42" max="43" width="15.140625" customWidth="1"/>
-    <col min="44" max="44" width="19.42578125" customWidth="1"/>
-    <col min="45" max="45" width="18.42578125" customWidth="1"/>
-    <col min="46" max="46" width="17.140625" customWidth="1"/>
-    <col min="47" max="47" width="19.42578125" customWidth="1"/>
-    <col min="48" max="48" width="18.42578125" customWidth="1"/>
+    <col min="41" max="41" width="14.5" customWidth="1"/>
+    <col min="42" max="43" width="15.1640625" customWidth="1"/>
+    <col min="44" max="44" width="19.5" customWidth="1"/>
+    <col min="45" max="45" width="18.5" customWidth="1"/>
+    <col min="46" max="46" width="17.1640625" customWidth="1"/>
+    <col min="47" max="47" width="19.5" customWidth="1"/>
+    <col min="48" max="48" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -926,7 +926,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>95</v>
       </c>
@@ -1075,7 +1075,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>96</v>
       </c>
@@ -1224,7 +1224,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>97</v>
       </c>
@@ -1373,7 +1373,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="5" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -1537,7 +1537,7 @@
         <v>#N/A</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -1576,7 +1576,7 @@
         <v>30</v>
       </c>
       <c r="R6">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S6" t="b">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>64</v>
       </c>
@@ -1686,7 +1686,7 @@
         <v>#N/A</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
         <v>10</v>
@@ -1725,7 +1725,7 @@
         <v>30</v>
       </c>
       <c r="R7">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="S7" t="b">
         <v>0</v>
@@ -1821,7 +1821,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="8" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>99</v>
       </c>
@@ -1970,7 +1970,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="9" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>100</v>
       </c>
@@ -2119,7 +2119,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="10" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>101</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="11" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>102</v>
       </c>
@@ -2417,7 +2417,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="12" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>103</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D12" t="e">
         <v>#N/A</v>
@@ -2461,7 +2461,7 @@
         <v>300</v>
       </c>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
         <v>1</v>
@@ -2470,7 +2470,7 @@
         <v>30</v>
       </c>
       <c r="R12">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="S12" t="b">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>50</v>
       </c>
       <c r="Z12">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA12">
         <v>3</v>
@@ -2566,7 +2566,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="13" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>104</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D13" t="e">
         <v>#N/A</v>
@@ -2610,7 +2610,7 @@
         <v>300</v>
       </c>
       <c r="O13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P13">
         <v>1</v>
@@ -2619,7 +2619,7 @@
         <v>30</v>
       </c>
       <c r="R13">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="S13" t="b">
         <v>0</v>
@@ -2643,7 +2643,7 @@
         <v>50</v>
       </c>
       <c r="Z13">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA13">
         <v>3</v>
@@ -2715,7 +2715,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="14" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>105</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D14" t="e">
         <v>#N/A</v>
@@ -2768,7 +2768,7 @@
         <v>30</v>
       </c>
       <c r="R14">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="S14" t="b">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         <v>50</v>
       </c>
       <c r="Z14">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA14">
         <v>3</v>
@@ -2864,7 +2864,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>106</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D15" t="e">
         <v>#N/A</v>
@@ -2908,7 +2908,7 @@
         <v>300</v>
       </c>
       <c r="O15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P15">
         <v>1</v>
@@ -2917,7 +2917,7 @@
         <v>30</v>
       </c>
       <c r="R15">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="S15" t="b">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>50</v>
       </c>
       <c r="Z15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA15">
         <v>3</v>
@@ -3013,7 +3013,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>107</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="D16" t="e">
         <v>#N/A</v>
@@ -3057,7 +3057,7 @@
         <v>300</v>
       </c>
       <c r="O16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16">
         <v>1</v>
@@ -3066,7 +3066,7 @@
         <v>30</v>
       </c>
       <c r="R16">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="S16" t="b">
         <v>0</v>
@@ -3090,7 +3090,7 @@
         <v>50</v>
       </c>
       <c r="Z16">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AA16">
         <v>3</v>
@@ -3162,7 +3162,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>65</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
@@ -3476,7 +3476,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>71</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="21" spans="1:49" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" ht="37" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>73</v>
       </c>
@@ -3947,7 +3947,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="22" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>74</v>
       </c>
@@ -4104,7 +4104,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="23" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>75</v>
       </c>
@@ -4261,7 +4261,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="24" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>76</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="25" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>77</v>
       </c>
@@ -4575,7 +4575,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="26" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>78</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="27" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>79</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="28" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>81</v>
       </c>
@@ -5046,7 +5046,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="29" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>82</v>
       </c>
@@ -5204,7 +5204,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="30" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>83</v>
       </c>
@@ -5362,7 +5362,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="31" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>85</v>
       </c>
@@ -5520,7 +5520,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="32" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>86</v>
       </c>
@@ -5677,7 +5677,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="33" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>87</v>
       </c>
@@ -5834,7 +5834,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="34" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>89</v>
       </c>
@@ -5991,7 +5991,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="35" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>90</v>
       </c>
@@ -6148,7 +6148,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="36" spans="1:49" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:49" ht="38" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>92</v>
       </c>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1117,7 +1117,28 @@
         <v>0.8</v>
       </c>
       <c r="AK6" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL6" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN6" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP6" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR6" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS6" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU6" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV6" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="7">
@@ -1227,7 +1248,28 @@
         <v>0.8</v>
       </c>
       <c r="AK7" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL7" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN7" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP7" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR7" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS7" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU7" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV7" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="8">
@@ -1337,7 +1379,31 @@
         <v>0.8</v>
       </c>
       <c r="AK8" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL8" t="str">
+        <v>Zapit</v>
+      </c>
+      <c r="AM8" t="str">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP8" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR8" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS8" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU8" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV8" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="9">
@@ -1447,7 +1513,31 @@
         <v>0.8</v>
       </c>
       <c r="AK9" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL9" t="str">
+        <v>Zapit</v>
+      </c>
+      <c r="AM9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP9" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR9" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS9" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU9" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV9" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="10">
@@ -1557,7 +1647,31 @@
         <v>0.8</v>
       </c>
       <c r="AK10" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL10" t="str">
+        <v>Zapit</v>
+      </c>
+      <c r="AM10" t="str">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP10" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR10" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS10" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU10" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV10" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="11">
@@ -1667,7 +1781,31 @@
         <v>0.8</v>
       </c>
       <c r="AK11" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL11" t="str">
+        <v>Zapit</v>
+      </c>
+      <c r="AM11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP11" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR11" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS11" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU11" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV11" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="12">
@@ -1777,7 +1915,31 @@
         <v>0.8</v>
       </c>
       <c r="AK12" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL12" t="str">
+        <v>Zapit</v>
+      </c>
+      <c r="AM12" t="str">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR12" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS12" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU12" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV12" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="13">
@@ -1887,7 +2049,28 @@
         <v>0.8</v>
       </c>
       <c r="AK13" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL13" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN13" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP13" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR13" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS13" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU13" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV13" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="14">
@@ -1997,7 +2180,28 @@
         <v>0.8</v>
       </c>
       <c r="AK14" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL14" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN14" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP14" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR14" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS14" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU14" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV14" t="str">
+        <v>PPC</v>
       </c>
     </row>
     <row r="15">
@@ -2107,7 +2311,28 @@
         <v>0.8</v>
       </c>
       <c r="AK15" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
+      </c>
+      <c r="AL15" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN15" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP15" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR15" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS15" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU15" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV15" t="str">
+        <v>PPC</v>
       </c>
     </row>
   </sheetData>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW25"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1024,7 +1024,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1051,7 +1051,7 @@
         <v>300</v>
       </c>
       <c r="O6" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P6" t="str">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>0.8</v>
       </c>
       <c r="AK6" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL6" t="str">
         <v>Fiber</v>
@@ -1155,7 +1155,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1182,7 +1182,7 @@
         <v>300</v>
       </c>
       <c r="O7" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P7" t="str">
         <v>1</v>
@@ -1248,7 +1248,7 @@
         <v>0.8</v>
       </c>
       <c r="AK7" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL7" t="str">
         <v>Fiber</v>
@@ -1286,7 +1286,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1379,7 +1379,7 @@
         <v>0.8</v>
       </c>
       <c r="AK8" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL8" t="str">
         <v>Zapit</v>
@@ -1420,7 +1420,7 @@
         <v>FALSE</v>
       </c>
       <c r="F9" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G9" t="str">
         <v>WN</v>
@@ -1513,7 +1513,7 @@
         <v>0.8</v>
       </c>
       <c r="AK9" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL9" t="str">
         <v>Zapit</v>
@@ -1554,7 +1554,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1647,7 +1647,7 @@
         <v>0.8</v>
       </c>
       <c r="AK10" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL10" t="str">
         <v>Zapit</v>
@@ -1781,7 +1781,7 @@
         <v>0.8</v>
       </c>
       <c r="AK11" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL11" t="str">
         <v>Zapit</v>
@@ -1822,7 +1822,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -1915,7 +1915,7 @@
         <v>0.8</v>
       </c>
       <c r="AK12" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL12" t="str">
         <v>Zapit</v>
@@ -1983,7 +1983,7 @@
         <v>300</v>
       </c>
       <c r="O13" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P13" t="str">
         <v>1</v>
@@ -2049,7 +2049,7 @@
         <v>0.8</v>
       </c>
       <c r="AK13" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL13" t="str">
         <v>Fiber</v>
@@ -2114,7 +2114,7 @@
         <v>300</v>
       </c>
       <c r="O14" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P14" t="str">
         <v>1</v>
@@ -2180,7 +2180,7 @@
         <v>0.8</v>
       </c>
       <c r="AK14" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL14" t="str">
         <v>Fiber</v>
@@ -2245,7 +2245,7 @@
         <v>300</v>
       </c>
       <c r="O15" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P15" t="str">
         <v>1</v>
@@ -2311,7 +2311,7 @@
         <v>0.8</v>
       </c>
       <c r="AK15" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL15" t="str">
         <v>Fiber</v>
@@ -2332,12 +2332,1322 @@
         <v>Bilateral</v>
       </c>
       <c r="AV15" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>SS14</v>
+      </c>
+      <c r="B16" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F16" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G16" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H16" t="str">
+        <v>2</v>
+      </c>
+      <c r="I16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L16" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N16" t="str">
+        <v>300</v>
+      </c>
+      <c r="O16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="P16" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>30</v>
+      </c>
+      <c r="R16" t="str">
+        <v>2</v>
+      </c>
+      <c r="S16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T16" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U16" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W16" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X16" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB16" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC16" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD16" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE16" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF16" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG16" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH16" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI16" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ16" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK16" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL16" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN16" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP16" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR16" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS16" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU16" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV16" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>SS15</v>
+      </c>
+      <c r="B17" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F17" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G17" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H17" t="str">
+        <v>2</v>
+      </c>
+      <c r="I17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N17" t="str">
+        <v>300</v>
+      </c>
+      <c r="O17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P17" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="str">
+        <v>30</v>
+      </c>
+      <c r="R17" t="str">
+        <v>2</v>
+      </c>
+      <c r="S17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T17" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U17" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W17" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X17" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA17" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB17" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC17" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD17" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE17" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF17" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG17" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH17" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI17" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ17" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK17" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL17" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN17" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP17" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR17" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS17" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU17" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV17" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>SS16</v>
+      </c>
+      <c r="B18" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F18" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G18" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H18" t="str">
+        <v>2</v>
+      </c>
+      <c r="I18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N18" t="str">
+        <v>300</v>
+      </c>
+      <c r="O18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P18" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="str">
+        <v>30</v>
+      </c>
+      <c r="R18" t="str">
+        <v>2</v>
+      </c>
+      <c r="S18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T18" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U18" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W18" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X18" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA18" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB18" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC18" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD18" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE18" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF18" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG18" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH18" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI18" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ18" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK18" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL18" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN18" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP18" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR18" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS18" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU18" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV18" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>SS17</v>
+      </c>
+      <c r="B19" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F19" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G19" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H19" t="str">
+        <v>2</v>
+      </c>
+      <c r="I19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N19" t="str">
+        <v>300</v>
+      </c>
+      <c r="O19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="P19" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="str">
+        <v>30</v>
+      </c>
+      <c r="R19" t="str">
+        <v>2</v>
+      </c>
+      <c r="S19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T19" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U19" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W19" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X19" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA19" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB19" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC19" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE19" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF19" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG19" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH19" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI19" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ19" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK19" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL19" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN19" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP19" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR19" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS19" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU19" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV19" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>SS18</v>
+      </c>
+      <c r="B20" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G20" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H20" t="str">
+        <v>2</v>
+      </c>
+      <c r="I20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N20" t="str">
+        <v>300</v>
+      </c>
+      <c r="O20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="P20" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>30</v>
+      </c>
+      <c r="R20" t="str">
+        <v>2</v>
+      </c>
+      <c r="S20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T20" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U20" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W20" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X20" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA20" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB20" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC20" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD20" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE20" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF20" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG20" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH20" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI20" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ20" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK20" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL20" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN20" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP20" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR20" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS20" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU20" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV20" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>SS19</v>
+      </c>
+      <c r="B21" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F21" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G21" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H21" t="str">
+        <v>2</v>
+      </c>
+      <c r="I21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N21" t="str">
+        <v>300</v>
+      </c>
+      <c r="O21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P21" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>30</v>
+      </c>
+      <c r="R21" t="str">
+        <v>2</v>
+      </c>
+      <c r="S21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T21" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U21" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W21" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X21" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA21" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB21" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC21" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD21" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE21" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF21" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG21" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH21" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI21" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ21" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK21" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL21" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN21" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP21" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR21" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS21" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU21" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV21" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>SS20</v>
+      </c>
+      <c r="B22" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G22" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2</v>
+      </c>
+      <c r="I22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N22" t="str">
+        <v>300</v>
+      </c>
+      <c r="O22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="P22" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>30</v>
+      </c>
+      <c r="R22" t="str">
+        <v>2</v>
+      </c>
+      <c r="S22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T22" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U22" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W22" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X22" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z22" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB22" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC22" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD22" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE22" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF22" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG22" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH22" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI22" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ22" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK22" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL22" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN22" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP22" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR22" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS22" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU22" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV22" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>SS21</v>
+      </c>
+      <c r="B23" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C23" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F23" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G23" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H23" t="str">
+        <v>2</v>
+      </c>
+      <c r="I23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K23" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N23" t="str">
+        <v>300</v>
+      </c>
+      <c r="O23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P23" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>30</v>
+      </c>
+      <c r="R23" t="str">
+        <v>2</v>
+      </c>
+      <c r="S23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T23" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U23" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W23" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X23" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y23" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z23" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA23" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB23" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC23" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD23" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE23" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF23" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG23" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH23" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI23" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ23" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK23" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL23" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN23" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP23" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR23" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS23" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU23" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV23" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>SS22</v>
+      </c>
+      <c r="B24" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C24" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G24" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H24" t="str">
+        <v>2</v>
+      </c>
+      <c r="I24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K24" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N24" t="str">
+        <v>300</v>
+      </c>
+      <c r="O24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P24" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q24" t="str">
+        <v>30</v>
+      </c>
+      <c r="R24" t="str">
+        <v>2</v>
+      </c>
+      <c r="S24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T24" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U24" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W24" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X24" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z24" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB24" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC24" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD24" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE24" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF24" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG24" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH24" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI24" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ24" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK24" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL24" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN24" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP24" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR24" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS24" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU24" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV24" t="str">
+        <v>PPC</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>SS23</v>
+      </c>
+      <c r="B25" t="str">
+        <v>SOUND_CAT</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Full_Task_Cont</v>
+      </c>
+      <c r="E25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="F25" t="str">
+        <v>Habituation</v>
+      </c>
+      <c r="G25" t="str">
+        <v>WN</v>
+      </c>
+      <c r="H25" t="str">
+        <v>2</v>
+      </c>
+      <c r="I25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="J25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="K25" t="str">
+        <v>Low_Left_High_Right</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Low_Pro_High_Anti</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Fixed</v>
+      </c>
+      <c r="N25" t="str">
+        <v>300</v>
+      </c>
+      <c r="O25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="P25" t="str">
+        <v>1</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>30</v>
+      </c>
+      <c r="R25" t="str">
+        <v>2</v>
+      </c>
+      <c r="S25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="T25" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="U25" t="str">
+        <v>0.5</v>
+      </c>
+      <c r="V25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="W25" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="X25" t="str">
+        <v>50</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>50</v>
+      </c>
+      <c r="Z25" t="str">
+        <v>10</v>
+      </c>
+      <c r="AA25" t="str">
+        <v>3</v>
+      </c>
+      <c r="AB25" t="str">
+        <v>10</v>
+      </c>
+      <c r="AC25" t="str">
+        <v>50</v>
+      </c>
+      <c r="AD25" t="str">
+        <v>82</v>
+      </c>
+      <c r="AE25" t="str">
+        <v>300</v>
+      </c>
+      <c r="AF25" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG25" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AH25" t="str">
+        <v>20</v>
+      </c>
+      <c r="AI25" t="str">
+        <v>3</v>
+      </c>
+      <c r="AJ25" t="str">
+        <v>0.8</v>
+      </c>
+      <c r="AK25" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AL25" t="str">
+        <v>Fiber</v>
+      </c>
+      <c r="AN25" t="str">
+        <v>30</v>
+      </c>
+      <c r="AP25" t="str">
+        <v>Sound</v>
+      </c>
+      <c r="AR25" t="str">
+        <v>Feedback</v>
+      </c>
+      <c r="AS25" t="str">
+        <v>Inter_Trial_Interval</v>
+      </c>
+      <c r="AU25" t="str">
+        <v>Bilateral</v>
+      </c>
+      <c r="AV25" t="str">
         <v>PPC</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AW15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AW25"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1688,7 +1688,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -2084,10 +2084,10 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E14" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>
@@ -2215,16 +2215,16 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E15" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>
       </c>
       <c r="H15" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I15" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1031" uniqueCount="109">
   <si>
     <t>Subject</t>
   </si>
@@ -196,34 +196,34 @@
     <t>Fixed</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>1.75</t>
+  </si>
+  <si>
+    <t>0.8</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>82</t>
+  </si>
+  <si>
     <t>300</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>1.75</t>
-  </si>
-  <si>
-    <t>0.8</t>
-  </si>
-  <si>
-    <t>0.5</t>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>82</t>
   </si>
   <si>
     <t>20</t>
@@ -348,13 +348,19 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -365,7 +371,14 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -377,7 +390,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
@@ -385,7 +398,13 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
@@ -693,55 +712,55 @@
   <dimension ref="A1:AW25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="11" max="11" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="12" max="12" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="13" max="13" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="14" max="14" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="15" max="15" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="16" max="16" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="17" max="17" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="18" max="18" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="19" max="19" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="20" max="20" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="21" max="21" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="22" max="22" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="23" max="23" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="24" max="24" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="25" max="25" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="26" max="26" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="27" max="27" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="28" max="28" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="29" max="29" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="30" max="30" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="31" max="31" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="32" max="32" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="33" max="33" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="34" max="34" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="35" max="35" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="36" max="36" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="37" max="37" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="38" max="38" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="39" max="39" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="40" max="40" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="41" max="41" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="42" max="42" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="43" max="43" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="44" max="44" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="45" max="45" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="46" max="46" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="47" max="47" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="48" max="48" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="49" max="49" style="3" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="5" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="17" max="17" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="18" max="18" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="19" max="19" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="20" max="20" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="21" max="21" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="22" max="22" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="23" max="23" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="24" max="24" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="25" max="25" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="26" max="26" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="27" max="27" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="28" max="28" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="29" max="29" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="30" max="30" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="31" max="31" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="32" max="32" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="33" max="33" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="34" max="34" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="35" max="35" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="36" max="36" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="37" max="37" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="38" max="38" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="39" max="39" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="40" max="40" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="41" max="41" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="42" max="42" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="43" max="43" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="44" max="44" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="45" max="45" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="46" max="46" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="47" max="47" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="48" max="48" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="49" max="49" style="4" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -784,7 +803,7 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
       <c r="O1" s="1" t="s">
@@ -931,62 +950,62 @@
       <c r="M2" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="2">
+        <v>300</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R2" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="S2" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U2" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V2" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA2" s="1" t="s">
+      <c r="AC2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD2" s="1" t="s">
+      <c r="AE2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE2" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF2" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG2" s="1" t="s">
         <v>52</v>
@@ -995,10 +1014,10 @@
         <v>70</v>
       </c>
       <c r="AI2" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ2" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK2" s="1" t="s">
         <v>56</v>
@@ -1054,62 +1073,62 @@
       <c r="M3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="2">
+        <v>300</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O3" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="S3" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U3" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V3" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA3" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC3" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE3" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF3" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG3" s="1" t="s">
         <v>52</v>
@@ -1118,10 +1137,10 @@
         <v>70</v>
       </c>
       <c r="AI3" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ3" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK3" s="1" t="s">
         <v>56</v>
@@ -1177,62 +1196,62 @@
       <c r="M4" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="2">
+        <v>300</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O4" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q4" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="R4" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="S4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T4" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U4" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V4" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z4" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA4" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC4" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD4" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB4" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD4" s="1" t="s">
+      <c r="AE4" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE4" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF4" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG4" s="1" t="s">
         <v>52</v>
@@ -1241,10 +1260,10 @@
         <v>70</v>
       </c>
       <c r="AI4" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ4" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK4" s="1" t="s">
         <v>56</v>
@@ -1300,41 +1319,41 @@
       <c r="M5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="N5" s="2">
+        <v>300</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T5" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U5" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U5" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V5" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z5" s="1" t="s">
         <v>55</v>
@@ -1343,19 +1362,19 @@
         <v>78</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AD5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE5" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE5" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG5" s="1" t="s">
         <v>52</v>
@@ -1367,7 +1386,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK5" s="1" t="s">
         <v>56</v>
@@ -1377,7 +1396,7 @@
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO5" s="1"/>
       <c r="AP5" s="1" t="s">
@@ -1437,62 +1456,62 @@
       <c r="M6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N6" s="2">
+      <c r="N6" s="3">
         <v>150</v>
       </c>
       <c r="O6" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T6" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U6" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U6" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V6" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z6" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA6" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC6" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD6" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB6" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC6" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD6" s="1" t="s">
+      <c r="AE6" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE6" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG6" s="1" t="s">
         <v>52</v>
@@ -1501,10 +1520,10 @@
         <v>70</v>
       </c>
       <c r="AI6" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK6" s="1" t="s">
         <v>56</v>
@@ -1514,7 +1533,7 @@
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO6" s="1"/>
       <c r="AP6" s="1" t="s">
@@ -1574,62 +1593,62 @@
       <c r="M7" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N7" s="2">
+      <c r="N7" s="3">
         <v>150</v>
       </c>
       <c r="O7" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T7" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U7" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z7" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC7" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD7" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD7" s="1" t="s">
+      <c r="AE7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE7" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG7" s="1" t="s">
         <v>52</v>
@@ -1638,10 +1657,10 @@
         <v>70</v>
       </c>
       <c r="AI7" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ7" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK7" s="1" t="s">
         <v>56</v>
@@ -1651,7 +1670,7 @@
       </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO7" s="1"/>
       <c r="AP7" s="1" t="s">
@@ -1711,62 +1730,62 @@
       <c r="M8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N8" s="2">
+      <c r="N8" s="3">
         <v>150</v>
       </c>
       <c r="O8" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T8" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U8" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U8" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V8" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z8" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD8" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD8" s="1" t="s">
+      <c r="AE8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE8" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG8" s="1" t="s">
         <v>52</v>
@@ -1775,10 +1794,10 @@
         <v>70</v>
       </c>
       <c r="AI8" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ8" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK8" s="1" t="s">
         <v>56</v>
@@ -1787,10 +1806,10 @@
         <v>91</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AN8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO8" s="1"/>
       <c r="AP8" s="1" t="s">
@@ -1850,62 +1869,62 @@
       <c r="M9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N9" s="2">
+      <c r="N9" s="3">
         <v>150</v>
       </c>
       <c r="O9" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S9" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U9" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U9" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V9" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z9" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD9" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB9" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC9" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD9" s="1" t="s">
+      <c r="AE9" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE9" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG9" s="1" t="s">
         <v>52</v>
@@ -1914,10 +1933,10 @@
         <v>70</v>
       </c>
       <c r="AI9" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ9" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK9" s="1" t="s">
         <v>56</v>
@@ -1926,10 +1945,10 @@
         <v>91</v>
       </c>
       <c r="AM9" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AN9" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO9" s="1"/>
       <c r="AP9" s="1" t="s">
@@ -1989,62 +2008,62 @@
       <c r="M10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N10" s="2">
+      <c r="N10" s="3">
         <v>150</v>
       </c>
       <c r="O10" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S10" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U10" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V10" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z10" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA10" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC10" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB10" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD10" s="1" t="s">
+      <c r="AE10" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE10" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG10" s="1" t="s">
         <v>52</v>
@@ -2053,10 +2072,10 @@
         <v>70</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK10" s="1" t="s">
         <v>56</v>
@@ -2065,10 +2084,10 @@
         <v>91</v>
       </c>
       <c r="AM10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AN10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO10" s="1"/>
       <c r="AP10" s="1" t="s">
@@ -2128,62 +2147,62 @@
       <c r="M11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="2">
+      <c r="N11" s="3">
         <v>150</v>
       </c>
       <c r="O11" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S11" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T11" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U11" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U11" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V11" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z11" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD11" s="1" t="s">
+      <c r="AE11" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE11" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG11" s="1" t="s">
         <v>52</v>
@@ -2192,10 +2211,10 @@
         <v>70</v>
       </c>
       <c r="AI11" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ11" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK11" s="1" t="s">
         <v>56</v>
@@ -2204,10 +2223,10 @@
         <v>91</v>
       </c>
       <c r="AM11" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AN11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO11" s="1"/>
       <c r="AP11" s="1" t="s">
@@ -2267,62 +2286,62 @@
       <c r="M12" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="2">
+      <c r="N12" s="3">
         <v>150</v>
       </c>
       <c r="O12" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V12" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC12" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD12" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB12" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC12" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD12" s="1" t="s">
+      <c r="AE12" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE12" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG12" s="1" t="s">
         <v>52</v>
@@ -2331,10 +2350,10 @@
         <v>70</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK12" s="1" t="s">
         <v>56</v>
@@ -2343,10 +2362,10 @@
         <v>91</v>
       </c>
       <c r="AM12" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AN12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO12" s="1"/>
       <c r="AP12" s="1" t="s">
@@ -2406,62 +2425,62 @@
       <c r="M13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N13" s="2">
+      <c r="N13" s="3">
         <v>150</v>
       </c>
       <c r="O13" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U13" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U13" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V13" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z13" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB13" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB13" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC13" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD13" s="1" t="s">
+      <c r="AE13" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE13" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG13" s="1" t="s">
         <v>52</v>
@@ -2470,10 +2489,10 @@
         <v>70</v>
       </c>
       <c r="AI13" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ13" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK13" s="1" t="s">
         <v>56</v>
@@ -2483,7 +2502,7 @@
       </c>
       <c r="AM13" s="1"/>
       <c r="AN13" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO13" s="1"/>
       <c r="AP13" s="1" t="s">
@@ -2543,62 +2562,62 @@
       <c r="M14" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N14" s="2">
+      <c r="N14" s="3">
         <v>150</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T14" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U14" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U14" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V14" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z14" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB14" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD14" s="1" t="s">
+      <c r="AE14" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE14" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG14" s="1" t="s">
         <v>52</v>
@@ -2607,10 +2626,10 @@
         <v>70</v>
       </c>
       <c r="AI14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ14" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK14" s="1" t="s">
         <v>56</v>
@@ -2620,7 +2639,7 @@
       </c>
       <c r="AM14" s="1"/>
       <c r="AN14" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO14" s="1"/>
       <c r="AP14" s="1" t="s">
@@ -2680,62 +2699,62 @@
       <c r="M15" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N15" s="2">
+      <c r="N15" s="3">
         <v>150</v>
       </c>
       <c r="O15" s="1" t="s">
         <v>52</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="T15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U15" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U15" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V15" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Z15" s="1" t="s">
         <v>55</v>
       </c>
       <c r="AA15" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB15" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AC15" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD15" s="1" t="s">
+      <c r="AE15" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE15" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG15" s="1" t="s">
         <v>52</v>
@@ -2744,10 +2763,10 @@
         <v>70</v>
       </c>
       <c r="AI15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK15" s="1" t="s">
         <v>56</v>
@@ -2757,7 +2776,7 @@
       </c>
       <c r="AM15" s="1"/>
       <c r="AN15" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO15" s="1"/>
       <c r="AP15" s="1" t="s">
@@ -2787,7 +2806,7 @@
         <v>50</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
@@ -2817,17 +2836,17 @@
       <c r="M16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N16" s="1" t="s">
+      <c r="N16" s="2">
+        <v>300</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O16" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R16" s="1" t="s">
         <v>55</v>
@@ -2836,43 +2855,43 @@
         <v>56</v>
       </c>
       <c r="T16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U16" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V16" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z16" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA16" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB16" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA16" s="1" t="s">
+      <c r="AC16" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB16" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC16" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD16" s="1" t="s">
+      <c r="AE16" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE16" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG16" s="1" t="s">
         <v>52</v>
@@ -2881,10 +2900,10 @@
         <v>70</v>
       </c>
       <c r="AI16" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ16" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK16" s="1" t="s">
         <v>56</v>
@@ -2894,7 +2913,7 @@
       </c>
       <c r="AM16" s="1"/>
       <c r="AN16" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO16" s="1"/>
       <c r="AP16" s="1" t="s">
@@ -2924,7 +2943,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
@@ -2954,17 +2973,17 @@
       <c r="M17" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="N17" s="2">
+        <v>300</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O17" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R17" s="1" t="s">
         <v>55</v>
@@ -2973,43 +2992,43 @@
         <v>56</v>
       </c>
       <c r="T17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U17" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U17" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V17" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z17" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA17" s="1" t="s">
+      <c r="AC17" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB17" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD17" s="1" t="s">
+      <c r="AE17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE17" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG17" s="1" t="s">
         <v>52</v>
@@ -3018,10 +3037,10 @@
         <v>70</v>
       </c>
       <c r="AI17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ17" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK17" s="1" t="s">
         <v>56</v>
@@ -3031,7 +3050,7 @@
       </c>
       <c r="AM17" s="1"/>
       <c r="AN17" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO17" s="1"/>
       <c r="AP17" s="1" t="s">
@@ -3061,7 +3080,7 @@
         <v>50</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
@@ -3091,17 +3110,17 @@
       <c r="M18" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N18" s="1" t="s">
+      <c r="N18" s="2">
+        <v>300</v>
+      </c>
+      <c r="O18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R18" s="1" t="s">
         <v>55</v>
@@ -3110,43 +3129,43 @@
         <v>56</v>
       </c>
       <c r="T18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U18" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U18" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V18" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z18" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA18" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB18" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA18" s="1" t="s">
+      <c r="AC18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB18" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC18" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD18" s="1" t="s">
+      <c r="AE18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE18" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG18" s="1" t="s">
         <v>52</v>
@@ -3155,10 +3174,10 @@
         <v>70</v>
       </c>
       <c r="AI18" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ18" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK18" s="1" t="s">
         <v>56</v>
@@ -3168,7 +3187,7 @@
       </c>
       <c r="AM18" s="1"/>
       <c r="AN18" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO18" s="1"/>
       <c r="AP18" s="1" t="s">
@@ -3198,7 +3217,7 @@
         <v>50</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
@@ -3228,17 +3247,17 @@
       <c r="M19" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N19" s="1" t="s">
+      <c r="N19" s="2">
+        <v>300</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R19" s="1" t="s">
         <v>55</v>
@@ -3247,43 +3266,43 @@
         <v>56</v>
       </c>
       <c r="T19" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U19" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U19" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V19" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z19" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB19" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA19" s="1" t="s">
+      <c r="AC19" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD19" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD19" s="1" t="s">
+      <c r="AE19" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE19" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG19" s="1" t="s">
         <v>52</v>
@@ -3292,10 +3311,10 @@
         <v>70</v>
       </c>
       <c r="AI19" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ19" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK19" s="1" t="s">
         <v>56</v>
@@ -3305,7 +3324,7 @@
       </c>
       <c r="AM19" s="1"/>
       <c r="AN19" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO19" s="1"/>
       <c r="AP19" s="1" t="s">
@@ -3335,7 +3354,7 @@
         <v>50</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
@@ -3365,17 +3384,17 @@
       <c r="M20" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N20" s="1" t="s">
+      <c r="N20" s="2">
+        <v>300</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O20" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q20" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>55</v>
@@ -3384,43 +3403,43 @@
         <v>56</v>
       </c>
       <c r="T20" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U20" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U20" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V20" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z20" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB20" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA20" s="1" t="s">
+      <c r="AC20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD20" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD20" s="1" t="s">
+      <c r="AE20" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE20" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF20" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG20" s="1" t="s">
         <v>52</v>
@@ -3429,10 +3448,10 @@
         <v>70</v>
       </c>
       <c r="AI20" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ20" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK20" s="1" t="s">
         <v>56</v>
@@ -3442,7 +3461,7 @@
       </c>
       <c r="AM20" s="1"/>
       <c r="AN20" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO20" s="1"/>
       <c r="AP20" s="1" t="s">
@@ -3472,7 +3491,7 @@
         <v>50</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
@@ -3502,17 +3521,17 @@
       <c r="M21" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N21" s="1" t="s">
+      <c r="N21" s="2">
+        <v>300</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O21" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R21" s="1" t="s">
         <v>55</v>
@@ -3521,43 +3540,43 @@
         <v>56</v>
       </c>
       <c r="T21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U21" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U21" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V21" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z21" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA21" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB21" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA21" s="1" t="s">
+      <c r="AC21" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD21" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD21" s="1" t="s">
+      <c r="AE21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE21" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG21" s="1" t="s">
         <v>52</v>
@@ -3566,10 +3585,10 @@
         <v>70</v>
       </c>
       <c r="AI21" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK21" s="1" t="s">
         <v>56</v>
@@ -3579,7 +3598,7 @@
       </c>
       <c r="AM21" s="1"/>
       <c r="AN21" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO21" s="1"/>
       <c r="AP21" s="1" t="s">
@@ -3609,7 +3628,7 @@
         <v>50</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
@@ -3639,17 +3658,17 @@
       <c r="M22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N22" s="1" t="s">
+      <c r="N22" s="2">
+        <v>300</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R22" s="1" t="s">
         <v>55</v>
@@ -3658,43 +3677,43 @@
         <v>56</v>
       </c>
       <c r="T22" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U22" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V22" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z22" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA22" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB22" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA22" s="1" t="s">
+      <c r="AC22" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD22" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC22" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD22" s="1" t="s">
+      <c r="AE22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE22" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG22" s="1" t="s">
         <v>52</v>
@@ -3703,10 +3722,10 @@
         <v>70</v>
       </c>
       <c r="AI22" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK22" s="1" t="s">
         <v>56</v>
@@ -3716,7 +3735,7 @@
       </c>
       <c r="AM22" s="1"/>
       <c r="AN22" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO22" s="1"/>
       <c r="AP22" s="1" t="s">
@@ -3746,7 +3765,7 @@
         <v>50</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
@@ -3776,17 +3795,17 @@
       <c r="M23" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N23" s="1" t="s">
+      <c r="N23" s="2">
+        <v>300</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O23" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R23" s="1" t="s">
         <v>55</v>
@@ -3795,43 +3814,43 @@
         <v>56</v>
       </c>
       <c r="T23" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U23" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U23" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V23" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z23" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB23" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA23" s="1" t="s">
+      <c r="AC23" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD23" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC23" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD23" s="1" t="s">
+      <c r="AE23" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE23" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG23" s="1" t="s">
         <v>52</v>
@@ -3840,10 +3859,10 @@
         <v>70</v>
       </c>
       <c r="AI23" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ23" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK23" s="1" t="s">
         <v>56</v>
@@ -3853,7 +3872,7 @@
       </c>
       <c r="AM23" s="1"/>
       <c r="AN23" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO23" s="1"/>
       <c r="AP23" s="1" t="s">
@@ -3883,7 +3902,7 @@
         <v>50</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
@@ -3913,17 +3932,17 @@
       <c r="M24" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N24" s="1" t="s">
+      <c r="N24" s="2">
+        <v>300</v>
+      </c>
+      <c r="O24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R24" s="1" t="s">
         <v>55</v>
@@ -3932,43 +3951,43 @@
         <v>56</v>
       </c>
       <c r="T24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V24" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z24" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB24" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA24" s="1" t="s">
+      <c r="AC24" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD24" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB24" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD24" s="1" t="s">
+      <c r="AE24" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE24" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG24" s="1" t="s">
         <v>52</v>
@@ -3977,10 +3996,10 @@
         <v>70</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ24" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK24" s="1" t="s">
         <v>56</v>
@@ -3990,7 +4009,7 @@
       </c>
       <c r="AM24" s="1"/>
       <c r="AN24" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO24" s="1"/>
       <c r="AP24" s="1" t="s">
@@ -4020,7 +4039,7 @@
         <v>50</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
@@ -4050,17 +4069,17 @@
       <c r="M25" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N25" s="1" t="s">
+      <c r="N25" s="2">
+        <v>300</v>
+      </c>
+      <c r="O25" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O25" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="Q25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R25" s="1" t="s">
         <v>55</v>
@@ -4069,43 +4088,43 @@
         <v>56</v>
       </c>
       <c r="T25" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U25" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="U25" s="1" t="s">
-        <v>65</v>
-      </c>
       <c r="V25" s="1" t="s">
         <v>56</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="X25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z25" s="2">
+        <v>2</v>
+      </c>
+      <c r="AA25" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AB25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA25" s="1" t="s">
+      <c r="AC25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD25" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AB25" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AC25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD25" s="1" t="s">
+      <c r="AE25" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AE25" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="AF25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AG25" s="1" t="s">
         <v>52</v>
@@ -4114,10 +4133,10 @@
         <v>70</v>
       </c>
       <c r="AI25" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="AJ25" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AK25" s="1" t="s">
         <v>56</v>
@@ -4127,7 +4146,7 @@
       </c>
       <c r="AM25" s="1"/>
       <c r="AN25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AO25" s="1"/>
       <c r="AP25" s="1" t="s">

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -2342,7 +2342,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C16" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E16" t="str">
         <v>TRUE</v>
@@ -2354,7 +2354,7 @@
         <v>WN</v>
       </c>
       <c r="H16" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I16" t="str">
         <v>FALSE</v>
@@ -2473,7 +2473,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C17" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E17" t="str">
         <v>TRUE</v>
@@ -2485,7 +2485,7 @@
         <v>WN</v>
       </c>
       <c r="H17" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I17" t="str">
         <v>FALSE</v>
@@ -2604,7 +2604,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C18" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E18" t="str">
         <v>TRUE</v>
@@ -2616,7 +2616,7 @@
         <v>WN</v>
       </c>
       <c r="H18" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I18" t="str">
         <v>FALSE</v>
@@ -2735,7 +2735,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C19" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E19" t="str">
         <v>TRUE</v>
@@ -2747,7 +2747,7 @@
         <v>WN</v>
       </c>
       <c r="H19" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I19" t="str">
         <v>FALSE</v>
@@ -2866,7 +2866,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C20" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E20" t="str">
         <v>TRUE</v>
@@ -2878,7 +2878,7 @@
         <v>WN</v>
       </c>
       <c r="H20" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I20" t="str">
         <v>FALSE</v>
@@ -2997,7 +2997,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C21" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E21" t="str">
         <v>TRUE</v>
@@ -3009,7 +3009,7 @@
         <v>WN</v>
       </c>
       <c r="H21" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I21" t="str">
         <v>FALSE</v>
@@ -3128,7 +3128,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C22" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E22" t="str">
         <v>TRUE</v>
@@ -3140,7 +3140,7 @@
         <v>WN</v>
       </c>
       <c r="H22" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I22" t="str">
         <v>FALSE</v>
@@ -3259,7 +3259,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C23" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E23" t="str">
         <v>TRUE</v>
@@ -3271,7 +3271,7 @@
         <v>WN</v>
       </c>
       <c r="H23" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I23" t="str">
         <v>FALSE</v>
@@ -3390,7 +3390,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C24" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E24" t="str">
         <v>TRUE</v>
@@ -3402,7 +3402,7 @@
         <v>WN</v>
       </c>
       <c r="H24" t="str">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="I24" t="str">
         <v>FALSE</v>
@@ -3521,7 +3521,7 @@
         <v>SOUND_CAT</v>
       </c>
       <c r="C25" t="str">
-        <v>Three_And_Three</v>
+        <v>Full_Task_Cont</v>
       </c>
       <c r="E25" t="str">
         <v>TRUE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1023,7 +1023,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1154,7 +1154,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1285,7 +1285,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1419,7 +1419,7 @@
         <v>FALSE</v>
       </c>
       <c r="F9" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G9" t="str">
         <v>WN</v>
@@ -1553,7 +1553,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1687,7 +1687,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1821,7 +1821,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -2086,7 +2086,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>
@@ -2217,7 +2217,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>
@@ -2384,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="R16" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S16" t="str">
         <v>FALSE</v>
@@ -2515,7 +2515,7 @@
         <v>30</v>
       </c>
       <c r="R17" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="str">
         <v>FALSE</v>
@@ -2646,7 +2646,7 @@
         <v>30</v>
       </c>
       <c r="R18" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S18" t="str">
         <v>FALSE</v>
@@ -2777,7 +2777,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="str">
         <v>FALSE</v>
@@ -2908,7 +2908,7 @@
         <v>30</v>
       </c>
       <c r="R20" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="str">
         <v>FALSE</v>
@@ -3039,7 +3039,7 @@
         <v>30</v>
       </c>
       <c r="R21" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S21" t="str">
         <v>FALSE</v>
@@ -3170,7 +3170,7 @@
         <v>30</v>
       </c>
       <c r="R22" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S22" t="str">
         <v>FALSE</v>
@@ -3301,7 +3301,7 @@
         <v>30</v>
       </c>
       <c r="R23" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="str">
         <v>FALSE</v>
@@ -3432,7 +3432,7 @@
         <v>30</v>
       </c>
       <c r="R24" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S24" t="str">
         <v>FALSE</v>
@@ -3563,7 +3563,7 @@
         <v>30</v>
       </c>
       <c r="R25" t="str">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -2372,7 +2372,7 @@
         <v>Fixed</v>
       </c>
       <c r="N16" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O16" t="str">
         <v>FALSE</v>
@@ -2384,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="R16" t="str">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S16" t="str">
         <v>FALSE</v>
@@ -2503,7 +2503,7 @@
         <v>Fixed</v>
       </c>
       <c r="N17" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O17" t="str">
         <v>TRUE</v>
@@ -2515,7 +2515,7 @@
         <v>30</v>
       </c>
       <c r="R17" t="str">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="S17" t="str">
         <v>FALSE</v>
@@ -2634,7 +2634,7 @@
         <v>Fixed</v>
       </c>
       <c r="N18" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O18" t="str">
         <v>TRUE</v>
@@ -2646,7 +2646,7 @@
         <v>30</v>
       </c>
       <c r="R18" t="str">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="S18" t="str">
         <v>FALSE</v>
@@ -2896,7 +2896,7 @@
         <v>Fixed</v>
       </c>
       <c r="N20" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O20" t="str">
         <v>FALSE</v>
@@ -2908,7 +2908,7 @@
         <v>30</v>
       </c>
       <c r="R20" t="str">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S20" t="str">
         <v>FALSE</v>
@@ -3158,7 +3158,7 @@
         <v>Fixed</v>
       </c>
       <c r="N22" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O22" t="str">
         <v>FALSE</v>
@@ -3289,7 +3289,7 @@
         <v>Fixed</v>
       </c>
       <c r="N23" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O23" t="str">
         <v>TRUE</v>
@@ -3301,7 +3301,7 @@
         <v>30</v>
       </c>
       <c r="R23" t="str">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="S23" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1059,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="R6" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S6" t="str">
         <v>FALSE</v>
@@ -1190,7 +1190,7 @@
         <v>30</v>
       </c>
       <c r="R7" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S7" t="str">
         <v>FALSE</v>
@@ -1321,7 +1321,7 @@
         <v>30</v>
       </c>
       <c r="R8" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="str">
         <v>FALSE</v>
@@ -1455,7 +1455,7 @@
         <v>30</v>
       </c>
       <c r="R9" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S9" t="str">
         <v>FALSE</v>
@@ -1589,7 +1589,7 @@
         <v>30</v>
       </c>
       <c r="R10" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S10" t="str">
         <v>FALSE</v>
@@ -1723,7 +1723,7 @@
         <v>30</v>
       </c>
       <c r="R11" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="str">
         <v>FALSE</v>
@@ -1857,7 +1857,7 @@
         <v>30</v>
       </c>
       <c r="R12" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="str">
         <v>FALSE</v>
@@ -1991,7 +1991,7 @@
         <v>30</v>
       </c>
       <c r="R13" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="str">
         <v>FALSE</v>
@@ -2122,7 +2122,7 @@
         <v>30</v>
       </c>
       <c r="R14" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="str">
         <v>FALSE</v>
@@ -2253,7 +2253,7 @@
         <v>30</v>
       </c>
       <c r="R15" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="str">
         <v>FALSE</v>
@@ -2345,7 +2345,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E16" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F16" t="str">
         <v>Uniform</v>
@@ -2384,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="R16" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S16" t="str">
         <v>FALSE</v>
@@ -2476,7 +2476,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E17" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F17" t="str">
         <v>Uniform</v>
@@ -2515,7 +2515,7 @@
         <v>30</v>
       </c>
       <c r="R17" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="str">
         <v>FALSE</v>
@@ -2607,7 +2607,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E18" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F18" t="str">
         <v>Uniform</v>
@@ -2646,7 +2646,7 @@
         <v>30</v>
       </c>
       <c r="R18" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S18" t="str">
         <v>FALSE</v>
@@ -2765,7 +2765,7 @@
         <v>Fixed</v>
       </c>
       <c r="N19" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O19" t="str">
         <v>FALSE</v>
@@ -2777,7 +2777,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="str">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="S19" t="str">
         <v>FALSE</v>
@@ -2869,7 +2869,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E20" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F20" t="str">
         <v>Uniform</v>
@@ -2908,7 +2908,7 @@
         <v>30</v>
       </c>
       <c r="R20" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S20" t="str">
         <v>FALSE</v>
@@ -3131,7 +3131,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E22" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F22" t="str">
         <v>Uniform</v>
@@ -3170,7 +3170,7 @@
         <v>30</v>
       </c>
       <c r="R22" t="str">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="S22" t="str">
         <v>FALSE</v>
@@ -3262,7 +3262,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E23" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F23" t="str">
         <v>Uniform</v>
@@ -3301,7 +3301,7 @@
         <v>30</v>
       </c>
       <c r="R23" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S23" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -2345,7 +2345,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E16" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="F16" t="str">
         <v>Uniform</v>
@@ -2375,7 +2375,7 @@
         <v>150</v>
       </c>
       <c r="O16" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P16" t="str">
         <v>1</v>
@@ -2384,7 +2384,7 @@
         <v>30</v>
       </c>
       <c r="R16" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" t="str">
         <v>FALSE</v>
@@ -2476,7 +2476,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E17" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="F17" t="str">
         <v>Uniform</v>
@@ -2515,7 +2515,7 @@
         <v>30</v>
       </c>
       <c r="R17" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="str">
         <v>FALSE</v>
@@ -2703,10 +2703,10 @@
         <v>0.8</v>
       </c>
       <c r="AK18" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL18" t="str">
-        <v>Fiber</v>
+        <v>Zapit</v>
       </c>
       <c r="AN18" t="str">
         <v>30</v>
@@ -2768,7 +2768,7 @@
         <v>150</v>
       </c>
       <c r="O19" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P19" t="str">
         <v>1</v>
@@ -2777,7 +2777,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="str">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="str">
         <v>FALSE</v>
@@ -2869,7 +2869,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E20" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="F20" t="str">
         <v>Uniform</v>
@@ -2899,7 +2899,7 @@
         <v>150</v>
       </c>
       <c r="O20" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P20" t="str">
         <v>1</v>
@@ -2908,7 +2908,7 @@
         <v>30</v>
       </c>
       <c r="R20" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" t="str">
         <v>FALSE</v>
@@ -3131,7 +3131,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E22" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="F22" t="str">
         <v>Uniform</v>
@@ -3161,7 +3161,7 @@
         <v>150</v>
       </c>
       <c r="O22" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P22" t="str">
         <v>1</v>
@@ -3170,7 +3170,7 @@
         <v>30</v>
       </c>
       <c r="R22" t="str">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" t="str">
         <v>FALSE</v>
@@ -3358,10 +3358,10 @@
         <v>0.8</v>
       </c>
       <c r="AK23" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL23" t="str">
-        <v>Fiber</v>
+        <v>Zapit</v>
       </c>
       <c r="AN23" t="str">
         <v>30</v>
@@ -3524,7 +3524,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E25" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F25" t="str">
         <v>Uniform</v>
@@ -3551,7 +3551,7 @@
         <v>Fixed</v>
       </c>
       <c r="N25" t="str">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="O25" t="str">
         <v>TRUE</v>
@@ -3563,7 +3563,7 @@
         <v>30</v>
       </c>
       <c r="R25" t="str">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S25" t="str">
         <v>FALSE</v>
@@ -3620,10 +3620,10 @@
         <v>0.8</v>
       </c>
       <c r="AK25" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL25" t="str">
-        <v>Fiber</v>
+        <v>Zapit</v>
       </c>
       <c r="AN25" t="str">
         <v>30</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Serkan/Desktop/pro/PhD/main/repos/behaviour_rig/Params/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8F0C5DA-13A4-FA47-BC82-08525ECAD034}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA40E2C-EBFE-6F45-83A9-EB5200175BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="112">
   <si>
     <t>Subject</t>
   </si>
@@ -1339,10 +1339,10 @@
         <v>25</v>
       </c>
       <c r="AU5" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV5" t="s">
         <v>82</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="6" spans="1:49" x14ac:dyDescent="0.2">
@@ -1470,10 +1470,10 @@
         <v>25</v>
       </c>
       <c r="AU6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV6" t="s">
         <v>88</v>
-      </c>
-      <c r="AV6" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="7" spans="1:49" x14ac:dyDescent="0.2">
@@ -1601,10 +1601,10 @@
         <v>25</v>
       </c>
       <c r="AU7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV7" t="s">
         <v>88</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:49" x14ac:dyDescent="0.2">
@@ -1735,10 +1735,10 @@
         <v>25</v>
       </c>
       <c r="AU8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV8" t="s">
         <v>88</v>
-      </c>
-      <c r="AV8" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:49" x14ac:dyDescent="0.2">
@@ -1869,10 +1869,10 @@
         <v>25</v>
       </c>
       <c r="AU9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV9" t="s">
         <v>88</v>
-      </c>
-      <c r="AV9" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:49" x14ac:dyDescent="0.2">
@@ -2003,10 +2003,10 @@
         <v>25</v>
       </c>
       <c r="AU10" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV10" t="s">
         <v>88</v>
-      </c>
-      <c r="AV10" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:49" x14ac:dyDescent="0.2">
@@ -2137,10 +2137,10 @@
         <v>25</v>
       </c>
       <c r="AU11" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV11" t="s">
         <v>88</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="12" spans="1:49" x14ac:dyDescent="0.2">
@@ -2271,10 +2271,10 @@
         <v>25</v>
       </c>
       <c r="AU12" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV12" t="s">
         <v>88</v>
-      </c>
-      <c r="AV12" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="13" spans="1:49" x14ac:dyDescent="0.2">
@@ -2389,6 +2389,9 @@
       <c r="AL13" t="s">
         <v>79</v>
       </c>
+      <c r="AM13" t="s">
+        <v>61</v>
+      </c>
       <c r="AN13" t="s">
         <v>62</v>
       </c>
@@ -2402,10 +2405,10 @@
         <v>25</v>
       </c>
       <c r="AU13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV13" t="s">
         <v>88</v>
-      </c>
-      <c r="AV13" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:49" x14ac:dyDescent="0.2">
@@ -2520,6 +2523,9 @@
       <c r="AL14" t="s">
         <v>79</v>
       </c>
+      <c r="AM14" t="s">
+        <v>61</v>
+      </c>
       <c r="AN14" t="s">
         <v>62</v>
       </c>
@@ -2533,10 +2539,10 @@
         <v>25</v>
       </c>
       <c r="AU14" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV14" t="s">
         <v>88</v>
-      </c>
-      <c r="AV14" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:49" x14ac:dyDescent="0.2">
@@ -2651,6 +2657,9 @@
       <c r="AL15" t="s">
         <v>79</v>
       </c>
+      <c r="AM15" t="s">
+        <v>61</v>
+      </c>
       <c r="AN15" t="s">
         <v>62</v>
       </c>
@@ -2664,10 +2673,10 @@
         <v>25</v>
       </c>
       <c r="AU15" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV15" t="s">
         <v>88</v>
-      </c>
-      <c r="AV15" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="16" spans="1:49" x14ac:dyDescent="0.2">
@@ -2782,6 +2791,9 @@
       <c r="AL16" t="s">
         <v>79</v>
       </c>
+      <c r="AM16" t="s">
+        <v>61</v>
+      </c>
       <c r="AN16" t="s">
         <v>62</v>
       </c>
@@ -2795,10 +2807,10 @@
         <v>25</v>
       </c>
       <c r="AU16" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV16" t="s">
         <v>88</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="17" spans="1:48" x14ac:dyDescent="0.2">
@@ -2913,6 +2925,9 @@
       <c r="AL17" t="s">
         <v>79</v>
       </c>
+      <c r="AM17" t="s">
+        <v>61</v>
+      </c>
       <c r="AN17" t="s">
         <v>62</v>
       </c>
@@ -2926,10 +2941,10 @@
         <v>25</v>
       </c>
       <c r="AU17" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV17" t="s">
         <v>88</v>
-      </c>
-      <c r="AV17" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:48" x14ac:dyDescent="0.2">
@@ -3044,6 +3059,9 @@
       <c r="AL18" t="s">
         <v>93</v>
       </c>
+      <c r="AM18" t="s">
+        <v>61</v>
+      </c>
       <c r="AN18" t="s">
         <v>62</v>
       </c>
@@ -3057,10 +3075,10 @@
         <v>25</v>
       </c>
       <c r="AU18" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV18" t="s">
         <v>88</v>
-      </c>
-      <c r="AV18" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:48" x14ac:dyDescent="0.2">
@@ -3175,6 +3193,9 @@
       <c r="AL19" t="s">
         <v>79</v>
       </c>
+      <c r="AM19" t="s">
+        <v>61</v>
+      </c>
       <c r="AN19" t="s">
         <v>62</v>
       </c>
@@ -3188,10 +3209,10 @@
         <v>25</v>
       </c>
       <c r="AU19" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV19" t="s">
         <v>88</v>
-      </c>
-      <c r="AV19" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:48" x14ac:dyDescent="0.2">
@@ -3306,6 +3327,9 @@
       <c r="AL20" t="s">
         <v>79</v>
       </c>
+      <c r="AM20" t="s">
+        <v>61</v>
+      </c>
       <c r="AN20" t="s">
         <v>62</v>
       </c>
@@ -3319,10 +3343,10 @@
         <v>25</v>
       </c>
       <c r="AU20" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV20" t="s">
         <v>88</v>
-      </c>
-      <c r="AV20" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:48" x14ac:dyDescent="0.2">
@@ -3363,7 +3387,7 @@
         <v>59</v>
       </c>
       <c r="N21" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="O21" t="s">
         <v>52</v>
@@ -3437,6 +3461,9 @@
       <c r="AL21" t="s">
         <v>79</v>
       </c>
+      <c r="AM21" t="s">
+        <v>61</v>
+      </c>
       <c r="AN21" t="s">
         <v>62</v>
       </c>
@@ -3450,10 +3477,10 @@
         <v>25</v>
       </c>
       <c r="AU21" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV21" t="s">
         <v>88</v>
-      </c>
-      <c r="AV21" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="22" spans="1:48" x14ac:dyDescent="0.2">
@@ -3568,6 +3595,9 @@
       <c r="AL22" t="s">
         <v>79</v>
       </c>
+      <c r="AM22" t="s">
+        <v>61</v>
+      </c>
       <c r="AN22" t="s">
         <v>62</v>
       </c>
@@ -3581,10 +3611,10 @@
         <v>25</v>
       </c>
       <c r="AU22" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV22" t="s">
         <v>88</v>
-      </c>
-      <c r="AV22" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:48" x14ac:dyDescent="0.2">
@@ -3699,6 +3729,9 @@
       <c r="AL23" t="s">
         <v>93</v>
       </c>
+      <c r="AM23" t="s">
+        <v>61</v>
+      </c>
       <c r="AN23" t="s">
         <v>62</v>
       </c>
@@ -3712,10 +3745,10 @@
         <v>25</v>
       </c>
       <c r="AU23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV23" t="s">
         <v>88</v>
-      </c>
-      <c r="AV23" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="24" spans="1:48" x14ac:dyDescent="0.2">
@@ -3756,7 +3789,7 @@
         <v>59</v>
       </c>
       <c r="N24" t="s">
-        <v>60</v>
+        <v>86</v>
       </c>
       <c r="O24" t="s">
         <v>52</v>
@@ -3830,6 +3863,9 @@
       <c r="AL24" t="s">
         <v>79</v>
       </c>
+      <c r="AM24" t="s">
+        <v>61</v>
+      </c>
       <c r="AN24" t="s">
         <v>62</v>
       </c>
@@ -3843,10 +3879,10 @@
         <v>25</v>
       </c>
       <c r="AU24" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV24" t="s">
         <v>88</v>
-      </c>
-      <c r="AV24" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="25" spans="1:48" x14ac:dyDescent="0.2">
@@ -3961,6 +3997,9 @@
       <c r="AL25" t="s">
         <v>93</v>
       </c>
+      <c r="AM25" t="s">
+        <v>61</v>
+      </c>
       <c r="AN25" t="s">
         <v>62</v>
       </c>
@@ -3974,16 +4013,16 @@
         <v>25</v>
       </c>
       <c r="AU25" t="s">
+        <v>89</v>
+      </c>
+      <c r="AV25" t="s">
         <v>88</v>
-      </c>
-      <c r="AV25" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AW5 A8:AW11 A6:N6 P6:AW6 A7:N7 P7:AW7 A14:AW15 A12:N12 P12:AW12 A13:N13 P13:AW13 A18:AW25 A16:N16 P16:AW16 A17:N17 P17:AW17" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AW4 A11:AT11 A6:N6 P6:AT6 A7:N7 P7:AT7 A15:AL15 A12:N12 P12:AT12 A13:N13 P13:AL13 A25:AL25 A16:N16 P16:AL16 A17:N17 P17:AL17 AN13:AT13 A14:AL14 AN14:AT14 AN15:AT15 AN16:AT16 AN17:AT17 A18:AL18 AN18:AT18 A19:AL19 AN19:AT19 A20:AL20 AN20:AT20 A21:M21 AN21:AT21 A22:AL22 AN22:AT22 A23:AL23 AN23:AT23 A24:M24 AN24:AT24 AN25:AT25 A5:AT5 AW5 AW6 AW7 A8:AT8 AW8 A9:AT9 AW9 A10:AT10 AW10 AW11 AW12 AW13 AW14 AW15 AW16 AW17 AW18 AW19 AW20 AW21 AW22 AW23 AW24 AW25 O21:AL21 O24:AL24" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Serkan/Desktop/pro/PhD/main/repos/behaviour_rig/Params/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA40E2C-EBFE-6F45-83A9-EB5200175BF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A96260DD-A988-3644-8BDB-418FE6328FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2387,7 +2387,7 @@
         <v>56</v>
       </c>
       <c r="AL13" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AM13" t="s">
         <v>61</v>
@@ -2521,7 +2521,7 @@
         <v>56</v>
       </c>
       <c r="AL14" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AM14" t="s">
         <v>61</v>
@@ -2655,7 +2655,7 @@
         <v>56</v>
       </c>
       <c r="AL15" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AM15" t="s">
         <v>61</v>
@@ -2789,7 +2789,7 @@
         <v>56</v>
       </c>
       <c r="AL16" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AM16" t="s">
         <v>61</v>
@@ -2824,7 +2824,7 @@
         <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
         <v>53</v>
@@ -2863,7 +2863,7 @@
         <v>62</v>
       </c>
       <c r="R17" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="S17" t="s">
         <v>56</v>
@@ -2920,10 +2920,10 @@
         <v>64</v>
       </c>
       <c r="AK17" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AL17" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="AM17" t="s">
         <v>61</v>
@@ -3226,7 +3226,7 @@
         <v>76</v>
       </c>
       <c r="E20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F20" t="s">
         <v>53</v>
@@ -3265,7 +3265,7 @@
         <v>62</v>
       </c>
       <c r="R20" t="s">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="S20" t="s">
         <v>56</v>
@@ -3322,7 +3322,7 @@
         <v>64</v>
       </c>
       <c r="AK20" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="AL20" t="s">
         <v>79</v>
@@ -4022,7 +4022,7 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AW4 A11:AT11 A6:N6 P6:AT6 A7:N7 P7:AT7 A15:AL15 A12:N12 P12:AT12 A13:N13 P13:AL13 A25:AL25 A16:N16 P16:AL16 A17:N17 P17:AL17 AN13:AT13 A14:AL14 AN14:AT14 AN15:AT15 AN16:AT16 AN17:AT17 A18:AL18 AN18:AT18 A19:AL19 AN19:AT19 A20:AL20 AN20:AT20 A21:M21 AN21:AT21 A22:AL22 AN22:AT22 A23:AL23 AN23:AT23 A24:M24 AN24:AT24 AN25:AT25 A5:AT5 AW5 AW6 AW7 A8:AT8 AW8 A9:AT9 AW9 A10:AT10 AW10 AW11 AW12 AW13 AW14 AW15 AW16 AW17 AW18 AW19 AW20 AW21 AW22 AW23 AW24 AW25 O21:AL21 O24:AL24" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AW4 A11:AT11 A6:N6 P6:AT6 A7:N7 P7:AT7 A15:AK15 A12:N12 P12:AT12 A13:N13 P13:AK13 A25:AL25 A16:N16 P16:AK16 A17:D17 P17:Q17 AN13:AT13 A14:AK14 AN14:AT14 AN15:AT15 AN16:AT16 AN17:AT17 A18:AL18 AN18:AT18 A19:AL19 AN19:AT19 A20:D20 AN20:AT20 A21:M21 AN21:AT21 A22:AL22 AN22:AT22 A23:AL23 AN23:AT23 A24:M24 AN24:AT24 AN25:AT25 A5:AT5 AW5 AW6 AW7 A8:AT8 AW8 A9:AT9 AW9 A10:AT10 AW10 AW11 AW12 AW13 AW14 AW15 AW16 AW17 AW18 AW19 AW20 AW21 AW22 AW23 AW24 AW25 O21:AL21 O24:AL24 F17:N17 F20:Q20 S17:AJ17 S20:AJ20 AL20" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1023,7 +1023,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1154,7 +1154,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1285,7 +1285,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1419,7 +1419,7 @@
         <v>FALSE</v>
       </c>
       <c r="F9" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G9" t="str">
         <v>WN</v>
@@ -1553,7 +1553,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1687,7 +1687,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1821,7 +1821,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -2089,7 +2089,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>
@@ -2223,7 +2223,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>
@@ -2795,7 +2795,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="str">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="S19" t="str">
         <v>FALSE</v>
@@ -3254,7 +3254,7 @@
         <v>0.8</v>
       </c>
       <c r="AK22" t="str">
-        <v/>
+        <v>TRUE</v>
       </c>
       <c r="AL22" t="str">
         <v>Zapit</v>
@@ -3465,7 +3465,7 @@
         <v>30</v>
       </c>
       <c r="R24" t="str">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="S24" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -955,7 +955,7 @@
         <v>2</v>
       </c>
       <c r="AA5" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="str">
         <v>10</v>
@@ -988,7 +988,10 @@
         <v>FALSE</v>
       </c>
       <c r="AL5" t="str">
-        <v>Fiber</v>
+        <v>Zapit</v>
+      </c>
+      <c r="AM5" t="str">
+        <v>1</v>
       </c>
       <c r="AN5" t="str">
         <v>30</v>
@@ -1003,10 +1006,10 @@
         <v>Inter_Trial_Interval</v>
       </c>
       <c r="AU5" t="str">
-        <v>ALM</v>
+        <v>PPC</v>
       </c>
       <c r="AV5" t="str">
-        <v>Unilateral_Right</v>
+        <v>Bilateral</v>
       </c>
     </row>
     <row r="6">
@@ -1119,7 +1122,10 @@
         <v>FALSE</v>
       </c>
       <c r="AL6" t="str">
-        <v>Fiber</v>
+        <v>Zapit</v>
+      </c>
+      <c r="AM6" t="str">
+        <v>1</v>
       </c>
       <c r="AN6" t="str">
         <v>30</v>
@@ -1250,7 +1256,10 @@
         <v>FALSE</v>
       </c>
       <c r="AL7" t="str">
-        <v>Fiber</v>
+        <v>Zapit</v>
+      </c>
+      <c r="AM7" t="str">
+        <v>1</v>
       </c>
       <c r="AN7" t="str">
         <v>30</v>
@@ -3465,7 +3474,7 @@
         <v>30</v>
       </c>
       <c r="R24" t="str">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S24" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -3435,7 +3435,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E24" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F24" t="str">
         <v>Uniform</v>
@@ -3474,7 +3474,7 @@
         <v>30</v>
       </c>
       <c r="R24" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S24" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -2804,7 +2804,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="str">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="S19" t="str">
         <v>FALSE</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -2765,7 +2765,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E19" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F19" t="str">
         <v>Uniform</v>
@@ -2804,7 +2804,7 @@
         <v>30</v>
       </c>
       <c r="R19" t="str">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="str">
         <v>FALSE</v>
@@ -2861,7 +2861,7 @@
         <v>0.8</v>
       </c>
       <c r="AK19" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL19" t="str">
         <v>Zapit</v>
@@ -3531,7 +3531,7 @@
         <v>0.8</v>
       </c>
       <c r="AK24" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL24" t="str">
         <v>Zapit</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1428,7 +1428,7 @@
         <v>FALSE</v>
       </c>
       <c r="F9" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G9" t="str">
         <v>WN</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1696,7 +1696,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -2098,7 +2098,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>
@@ -2232,7 +2232,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -2232,7 +2232,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>
@@ -2459,7 +2459,7 @@
         <v>0.8</v>
       </c>
       <c r="AK16" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL16" t="str">
         <v>Zapit</v>
@@ -2593,7 +2593,7 @@
         <v>0.8</v>
       </c>
       <c r="AK17" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL17" t="str">
         <v>Zapit</v>
@@ -2727,7 +2727,7 @@
         <v>0.8</v>
       </c>
       <c r="AK18" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL18" t="str">
         <v>Zapit</v>
@@ -2995,7 +2995,7 @@
         <v>0.8</v>
       </c>
       <c r="AK20" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL20" t="str">
         <v>Zapit</v>
@@ -3263,7 +3263,7 @@
         <v>0.8</v>
       </c>
       <c r="AK22" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL22" t="str">
         <v>Zapit</v>
@@ -3397,7 +3397,7 @@
         <v>0.8</v>
       </c>
       <c r="AK23" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL23" t="str">
         <v>Zapit</v>
@@ -3665,7 +3665,7 @@
         <v>0.8</v>
       </c>
       <c r="AK25" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL25" t="str">
         <v>Zapit</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AW25"/>
+  <dimension ref="A1:AW15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1014,7 +1014,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SS01</v>
+        <v>SS14</v>
       </c>
       <c r="B6" t="str">
         <v>SOUND_CAT</v>
@@ -1026,13 +1026,13 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
       </c>
       <c r="H6" t="str">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I6" t="str">
         <v>FALSE</v>
@@ -1053,7 +1053,7 @@
         <v>150</v>
       </c>
       <c r="O6" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P6" t="str">
         <v>1</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SS04</v>
+        <v>SS15</v>
       </c>
       <c r="B7" t="str">
         <v>SOUND_CAT</v>
@@ -1160,13 +1160,13 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
       </c>
       <c r="H7" t="str">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="I7" t="str">
         <v>FALSE</v>
@@ -1187,7 +1187,7 @@
         <v>150</v>
       </c>
       <c r="O7" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P7" t="str">
         <v>1</v>
@@ -1282,7 +1282,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SS05</v>
+        <v>SS16</v>
       </c>
       <c r="B8" t="str">
         <v>SOUND_CAT</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SS06</v>
+        <v>SS17</v>
       </c>
       <c r="B9" t="str">
         <v>SOUND_CAT</v>
@@ -1428,7 +1428,7 @@
         <v>FALSE</v>
       </c>
       <c r="F9" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G9" t="str">
         <v>WN</v>
@@ -1521,7 +1521,7 @@
         <v>0.8</v>
       </c>
       <c r="AK9" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL9" t="str">
         <v>Zapit</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SS07</v>
+        <v>SS18</v>
       </c>
       <c r="B10" t="str">
         <v>SOUND_CAT</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SS08</v>
+        <v>SS19</v>
       </c>
       <c r="B11" t="str">
         <v>SOUND_CAT</v>
@@ -1693,10 +1693,10 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E11" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1732,7 +1732,7 @@
         <v>30</v>
       </c>
       <c r="R11" t="str">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S11" t="str">
         <v>FALSE</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SS09</v>
+        <v>SS20</v>
       </c>
       <c r="B12" t="str">
         <v>SOUND_CAT</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -1857,7 +1857,7 @@
         <v>150</v>
       </c>
       <c r="O12" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P12" t="str">
         <v>1</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SS10</v>
+        <v>SS21</v>
       </c>
       <c r="B13" t="str">
         <v>SOUND_CAT</v>
@@ -1961,7 +1961,7 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E13" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F13" t="str">
         <v>Uniform</v>
@@ -1991,7 +1991,7 @@
         <v>150</v>
       </c>
       <c r="O13" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="P13" t="str">
         <v>1</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SS11</v>
+        <v>SS22</v>
       </c>
       <c r="B14" t="str">
         <v>SOUND_CAT</v>
@@ -2098,7 +2098,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>
@@ -2191,7 +2191,7 @@
         <v>0.8</v>
       </c>
       <c r="AK14" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL14" t="str">
         <v>Zapit</v>
@@ -2220,7 +2220,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SS13</v>
+        <v>SS23</v>
       </c>
       <c r="B15" t="str">
         <v>SOUND_CAT</v>
@@ -2232,7 +2232,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Left</v>
+        <v>Uniform</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>
@@ -2349,1352 +2349,12 @@
         <v>PPC</v>
       </c>
       <c r="AV15" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>SS14</v>
-      </c>
-      <c r="B16" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F16" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G16" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H16" t="str">
-        <v>8</v>
-      </c>
-      <c r="I16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K16" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L16" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M16" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N16" t="str">
-        <v>150</v>
-      </c>
-      <c r="O16" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P16" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="str">
-        <v>30</v>
-      </c>
-      <c r="R16" t="str">
-        <v>0</v>
-      </c>
-      <c r="S16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T16" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U16" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W16" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X16" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y16" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z16" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA16" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB16" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC16" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD16" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE16" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF16" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG16" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH16" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI16" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ16" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK16" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL16" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM16" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN16" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP16" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR16" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS16" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU16" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV16" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>SS15</v>
-      </c>
-      <c r="B17" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F17" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G17" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H17" t="str">
-        <v>8</v>
-      </c>
-      <c r="I17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L17" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N17" t="str">
-        <v>150</v>
-      </c>
-      <c r="O17" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P17" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q17" t="str">
-        <v>30</v>
-      </c>
-      <c r="R17" t="str">
-        <v>0</v>
-      </c>
-      <c r="S17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T17" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U17" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W17" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X17" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y17" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z17" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA17" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB17" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC17" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD17" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE17" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF17" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG17" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH17" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI17" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ17" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK17" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL17" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM17" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN17" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP17" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR17" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS17" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU17" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV17" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>SS16</v>
-      </c>
-      <c r="B18" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G18" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H18" t="str">
-        <v>8</v>
-      </c>
-      <c r="I18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L18" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M18" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N18" t="str">
-        <v>150</v>
-      </c>
-      <c r="O18" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P18" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q18" t="str">
-        <v>30</v>
-      </c>
-      <c r="R18" t="str">
-        <v>0</v>
-      </c>
-      <c r="S18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T18" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U18" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W18" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X18" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y18" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z18" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA18" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB18" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC18" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD18" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE18" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF18" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG18" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH18" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI18" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ18" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK18" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL18" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM18" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN18" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP18" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR18" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS18" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU18" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV18" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>SS17</v>
-      </c>
-      <c r="B19" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C19" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E19" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F19" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G19" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H19" t="str">
-        <v>8</v>
-      </c>
-      <c r="I19" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J19" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K19" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L19" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M19" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N19" t="str">
-        <v>150</v>
-      </c>
-      <c r="O19" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P19" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q19" t="str">
-        <v>30</v>
-      </c>
-      <c r="R19" t="str">
-        <v>0</v>
-      </c>
-      <c r="S19" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T19" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U19" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V19" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W19" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X19" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y19" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z19" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA19" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB19" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC19" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD19" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE19" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF19" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG19" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH19" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI19" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ19" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK19" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AL19" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM19" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN19" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP19" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR19" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS19" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU19" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV19" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>SS18</v>
-      </c>
-      <c r="B20" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G20" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H20" t="str">
-        <v>8</v>
-      </c>
-      <c r="I20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K20" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L20" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M20" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N20" t="str">
-        <v>150</v>
-      </c>
-      <c r="O20" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P20" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q20" t="str">
-        <v>30</v>
-      </c>
-      <c r="R20" t="str">
-        <v>0</v>
-      </c>
-      <c r="S20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T20" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U20" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W20" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X20" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y20" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z20" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA20" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB20" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC20" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD20" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE20" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF20" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG20" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH20" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI20" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ20" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK20" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL20" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM20" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN20" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP20" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR20" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS20" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU20" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV20" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>SS19</v>
-      </c>
-      <c r="B21" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E21" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="F21" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G21" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H21" t="str">
-        <v>8</v>
-      </c>
-      <c r="I21" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J21" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K21" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L21" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M21" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N21" t="str">
-        <v>150</v>
-      </c>
-      <c r="O21" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P21" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q21" t="str">
-        <v>30</v>
-      </c>
-      <c r="R21" t="str">
-        <v>1.5</v>
-      </c>
-      <c r="S21" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T21" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U21" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V21" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W21" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X21" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y21" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z21" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA21" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB21" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC21" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD21" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE21" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF21" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG21" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH21" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI21" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ21" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK21" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL21" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM21" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN21" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP21" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR21" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS21" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU21" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV21" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>SS20</v>
-      </c>
-      <c r="B22" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G22" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H22" t="str">
-        <v>8</v>
-      </c>
-      <c r="I22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K22" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L22" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M22" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N22" t="str">
-        <v>150</v>
-      </c>
-      <c r="O22" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P22" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q22" t="str">
-        <v>30</v>
-      </c>
-      <c r="R22" t="str">
-        <v>0</v>
-      </c>
-      <c r="S22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T22" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U22" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W22" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X22" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y22" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z22" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA22" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB22" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC22" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD22" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE22" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF22" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG22" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH22" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI22" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ22" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK22" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL22" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM22" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN22" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP22" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR22" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS22" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU22" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV22" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v>SS21</v>
-      </c>
-      <c r="B23" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C23" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F23" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G23" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H23" t="str">
-        <v>8</v>
-      </c>
-      <c r="I23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K23" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L23" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M23" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N23" t="str">
-        <v>150</v>
-      </c>
-      <c r="O23" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P23" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q23" t="str">
-        <v>30</v>
-      </c>
-      <c r="R23" t="str">
-        <v>0</v>
-      </c>
-      <c r="S23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T23" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U23" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W23" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X23" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y23" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z23" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA23" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB23" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC23" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD23" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE23" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF23" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG23" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH23" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI23" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ23" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK23" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL23" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM23" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN23" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP23" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR23" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS23" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU23" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV23" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>SS22</v>
-      </c>
-      <c r="B24" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C24" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E24" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F24" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G24" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H24" t="str">
-        <v>8</v>
-      </c>
-      <c r="I24" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J24" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K24" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L24" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M24" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N24" t="str">
-        <v>150</v>
-      </c>
-      <c r="O24" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P24" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q24" t="str">
-        <v>30</v>
-      </c>
-      <c r="R24" t="str">
-        <v>0</v>
-      </c>
-      <c r="S24" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T24" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U24" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V24" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W24" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X24" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y24" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z24" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA24" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB24" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC24" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD24" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE24" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF24" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG24" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH24" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI24" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ24" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK24" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AL24" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM24" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN24" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP24" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR24" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS24" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU24" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV24" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>SS23</v>
-      </c>
-      <c r="B25" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Uniform</v>
-      </c>
-      <c r="G25" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H25" t="str">
-        <v>8</v>
-      </c>
-      <c r="I25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K25" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L25" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M25" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N25" t="str">
-        <v>150</v>
-      </c>
-      <c r="O25" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P25" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q25" t="str">
-        <v>30</v>
-      </c>
-      <c r="R25" t="str">
-        <v>0</v>
-      </c>
-      <c r="S25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T25" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U25" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W25" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X25" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y25" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z25" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA25" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB25" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC25" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD25" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE25" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF25" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG25" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH25" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI25" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ25" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK25" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="AL25" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM25" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN25" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP25" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR25" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS25" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU25" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV25" t="str">
         <v>Bilateral</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AW25"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AW15"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1119,7 +1119,7 @@
         <v>0.8</v>
       </c>
       <c r="AK6" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL6" t="str">
         <v>Zapit</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1253,7 +1253,7 @@
         <v>0.8</v>
       </c>
       <c r="AK7" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL7" t="str">
         <v>Zapit</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1387,7 +1387,7 @@
         <v>0.8</v>
       </c>
       <c r="AK8" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL8" t="str">
         <v>Zapit</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1655,7 +1655,7 @@
         <v>0.8</v>
       </c>
       <c r="AK10" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL10" t="str">
         <v>Zapit</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -1923,7 +1923,7 @@
         <v>0.8</v>
       </c>
       <c r="AK12" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL12" t="str">
         <v>Zapit</v>
@@ -1964,7 +1964,7 @@
         <v>FALSE</v>
       </c>
       <c r="F13" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G13" t="str">
         <v>WN</v>
@@ -2057,7 +2057,7 @@
         <v>0.8</v>
       </c>
       <c r="AK13" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL13" t="str">
         <v>Zapit</v>
@@ -2232,7 +2232,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Uniform</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>
@@ -2325,7 +2325,7 @@
         <v>0.8</v>
       </c>
       <c r="AK15" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL15" t="str">
         <v>Zapit</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -1964,7 +1964,7 @@
         <v>FALSE</v>
       </c>
       <c r="F13" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G13" t="str">
         <v>WN</v>
@@ -2232,7 +2232,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -1964,7 +1964,7 @@
         <v>FALSE</v>
       </c>
       <c r="F13" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G13" t="str">
         <v>WN</v>
@@ -2232,7 +2232,7 @@
         <v>FALSE</v>
       </c>
       <c r="F15" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G15" t="str">
         <v>WN</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AW15"/>
+  <dimension ref="A1:AW14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1684,7 +1684,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SS19</v>
+        <v>SS20</v>
       </c>
       <c r="B11" t="str">
         <v>SOUND_CAT</v>
@@ -1693,10 +1693,10 @@
         <v>Full_Task_Cont</v>
       </c>
       <c r="E11" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1732,7 +1732,7 @@
         <v>30</v>
       </c>
       <c r="R11" t="str">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S11" t="str">
         <v>FALSE</v>
@@ -1789,7 +1789,7 @@
         <v>0.8</v>
       </c>
       <c r="AK11" t="str">
-        <v>FALSE</v>
+        <v>TRUE</v>
       </c>
       <c r="AL11" t="str">
         <v>Zapit</v>
@@ -1818,7 +1818,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SS20</v>
+        <v>SS21</v>
       </c>
       <c r="B12" t="str">
         <v>SOUND_CAT</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SS21</v>
+        <v>SS22</v>
       </c>
       <c r="B13" t="str">
         <v>SOUND_CAT</v>
@@ -1964,7 +1964,7 @@
         <v>FALSE</v>
       </c>
       <c r="F13" t="str">
-        <v>Asym_Right</v>
+        <v>Uniform</v>
       </c>
       <c r="G13" t="str">
         <v>WN</v>
@@ -2086,7 +2086,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SS22</v>
+        <v>SS23</v>
       </c>
       <c r="B14" t="str">
         <v>SOUND_CAT</v>
@@ -2098,7 +2098,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Uniform</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>
@@ -2215,146 +2215,12 @@
         <v>PPC</v>
       </c>
       <c r="AV14" t="str">
-        <v>Bilateral</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>SS23</v>
-      </c>
-      <c r="B15" t="str">
-        <v>SOUND_CAT</v>
-      </c>
-      <c r="C15" t="str">
-        <v>Full_Task_Cont</v>
-      </c>
-      <c r="E15" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="F15" t="str">
-        <v>Asym_Right</v>
-      </c>
-      <c r="G15" t="str">
-        <v>WN</v>
-      </c>
-      <c r="H15" t="str">
-        <v>8</v>
-      </c>
-      <c r="I15" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="J15" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="K15" t="str">
-        <v>Low_Left_High_Right</v>
-      </c>
-      <c r="L15" t="str">
-        <v>Low_Pro_High_Anti</v>
-      </c>
-      <c r="M15" t="str">
-        <v>Fixed</v>
-      </c>
-      <c r="N15" t="str">
-        <v>150</v>
-      </c>
-      <c r="O15" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="P15" t="str">
-        <v>1</v>
-      </c>
-      <c r="Q15" t="str">
-        <v>30</v>
-      </c>
-      <c r="R15" t="str">
-        <v>0</v>
-      </c>
-      <c r="S15" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="T15" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="U15" t="str">
-        <v>0.5</v>
-      </c>
-      <c r="V15" t="str">
-        <v>FALSE</v>
-      </c>
-      <c r="W15" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="X15" t="str">
-        <v>50</v>
-      </c>
-      <c r="Y15" t="str">
-        <v>50</v>
-      </c>
-      <c r="Z15" t="str">
-        <v>2</v>
-      </c>
-      <c r="AA15" t="str">
-        <v>3</v>
-      </c>
-      <c r="AB15" t="str">
-        <v>10</v>
-      </c>
-      <c r="AC15" t="str">
-        <v>50</v>
-      </c>
-      <c r="AD15" t="str">
-        <v>82</v>
-      </c>
-      <c r="AE15" t="str">
-        <v>300</v>
-      </c>
-      <c r="AF15" t="str">
-        <v>30</v>
-      </c>
-      <c r="AG15" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AH15" t="str">
-        <v>20</v>
-      </c>
-      <c r="AI15" t="str">
-        <v>3</v>
-      </c>
-      <c r="AJ15" t="str">
-        <v>0.8</v>
-      </c>
-      <c r="AK15" t="str">
-        <v>TRUE</v>
-      </c>
-      <c r="AL15" t="str">
-        <v>Zapit</v>
-      </c>
-      <c r="AM15" t="str">
-        <v>1</v>
-      </c>
-      <c r="AN15" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP15" t="str">
-        <v>Sound</v>
-      </c>
-      <c r="AR15" t="str">
-        <v>Feedback</v>
-      </c>
-      <c r="AS15" t="str">
-        <v>Inter_Trial_Interval</v>
-      </c>
-      <c r="AU15" t="str">
-        <v>PPC</v>
-      </c>
-      <c r="AV15" t="str">
         <v>Bilateral</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AW15"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AW14"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1521,7 +1521,7 @@
         <v>0.8</v>
       </c>
       <c r="AK9" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL9" t="str">
         <v>Zapit</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1696,7 +1696,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -2057,7 +2057,7 @@
         <v>0.8</v>
       </c>
       <c r="AK13" t="str">
-        <v>TRUE</v>
+        <v>FALSE</v>
       </c>
       <c r="AL13" t="str">
         <v>Zapit</v>
@@ -2098,7 +2098,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1696,7 +1696,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -2098,7 +2098,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Right</v>
+        <v>Asym_Left</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -1026,7 +1026,7 @@
         <v>FALSE</v>
       </c>
       <c r="F6" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G6" t="str">
         <v>WN</v>
@@ -1160,7 +1160,7 @@
         <v>FALSE</v>
       </c>
       <c r="F7" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G7" t="str">
         <v>WN</v>
@@ -1294,7 +1294,7 @@
         <v>FALSE</v>
       </c>
       <c r="F8" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G8" t="str">
         <v>WN</v>
@@ -1562,7 +1562,7 @@
         <v>FALSE</v>
       </c>
       <c r="F10" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G10" t="str">
         <v>WN</v>
@@ -1696,7 +1696,7 @@
         <v>FALSE</v>
       </c>
       <c r="F11" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G11" t="str">
         <v>WN</v>
@@ -1830,7 +1830,7 @@
         <v>FALSE</v>
       </c>
       <c r="F12" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G12" t="str">
         <v>WN</v>
@@ -2098,7 +2098,7 @@
         <v>FALSE</v>
       </c>
       <c r="F14" t="str">
-        <v>Asym_Left</v>
+        <v>Asym_Right</v>
       </c>
       <c r="G14" t="str">
         <v>WN</v>

--- a/Params/Mouse_Room_Params.xlsx
+++ b/Params/Mouse_Room_Params.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AW14"/>
+  <dimension ref="A1:AX14"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -512,39 +512,42 @@
         <v>Opto_ON</v>
       </c>
       <c r="AL1" t="str">
+        <v>Laser_On</v>
+      </c>
+      <c r="AM1" t="str">
         <v>Opto_Type</v>
       </c>
-      <c r="AM1" t="str">
-        <v>Zapit_Nb_Conditions</v>
-      </c>
       <c r="AN1" t="str">
+        <v>conditionNum</v>
+      </c>
+      <c r="AO1" t="str">
         <v>Perc_Opto_Trials</v>
       </c>
-      <c r="AO1" t="str">
+      <c r="AP1" t="str">
         <v>Light_Freq (Hz)</v>
       </c>
-      <c r="AP1" t="str">
+      <c r="AQ1" t="str">
         <v>Opto_Onset_1</v>
       </c>
-      <c r="AQ1" t="str">
+      <c r="AR1" t="str">
         <v>Opto_Onset_2</v>
       </c>
-      <c r="AR1" t="str">
+      <c r="AS1" t="str">
         <v>Opto_Offset_1</v>
       </c>
-      <c r="AS1" t="str">
+      <c r="AT1" t="str">
         <v>Opto_Offset_2</v>
       </c>
-      <c r="AT1" t="str">
+      <c r="AU1" t="str">
         <v>Opto_Duration</v>
       </c>
-      <c r="AU1" t="str">
+      <c r="AV1" t="str">
         <v>Stimulation_Site</v>
       </c>
-      <c r="AV1" t="str">
+      <c r="AW1" t="str">
         <v>Stimulation_Type</v>
       </c>
-      <c r="AW1" t="str">
+      <c r="AX1" t="str">
         <v>Rig</v>
       </c>
     </row>
@@ -988,27 +991,30 @@
         <v>FALSE</v>
       </c>
       <c r="AL5" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM5" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM5" t="str">
-        <v>1</v>
-      </c>
       <c r="AN5" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP5" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ5" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR5" t="str">
+      <c r="AS5" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS5" t="str">
+      <c r="AT5" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU5" t="str">
+      <c r="AV5" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV5" t="str">
+      <c r="AW5" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1122,27 +1128,30 @@
         <v>TRUE</v>
       </c>
       <c r="AL6" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM6" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM6" t="str">
-        <v>1</v>
-      </c>
       <c r="AN6" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP6" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO6" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ6" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR6" t="str">
+      <c r="AS6" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS6" t="str">
+      <c r="AT6" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU6" t="str">
+      <c r="AV6" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV6" t="str">
+      <c r="AW6" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1256,27 +1265,30 @@
         <v>TRUE</v>
       </c>
       <c r="AL7" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM7" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM7" t="str">
-        <v>1</v>
-      </c>
       <c r="AN7" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP7" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO7" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ7" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR7" t="str">
+      <c r="AS7" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS7" t="str">
+      <c r="AT7" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU7" t="str">
+      <c r="AV7" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV7" t="str">
+      <c r="AW7" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1390,27 +1402,30 @@
         <v>TRUE</v>
       </c>
       <c r="AL8" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM8" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM8" t="str">
-        <v>1</v>
-      </c>
       <c r="AN8" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP8" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO8" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ8" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR8" t="str">
+      <c r="AS8" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS8" t="str">
+      <c r="AT8" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU8" t="str">
+      <c r="AV8" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV8" t="str">
+      <c r="AW8" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1524,27 +1539,30 @@
         <v>FALSE</v>
       </c>
       <c r="AL9" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AM9" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM9" t="str">
-        <v>1</v>
-      </c>
       <c r="AN9" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO9" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ9" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR9" t="str">
+      <c r="AS9" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS9" t="str">
+      <c r="AT9" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU9" t="str">
+      <c r="AV9" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV9" t="str">
+      <c r="AW9" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1658,27 +1676,30 @@
         <v>TRUE</v>
       </c>
       <c r="AL10" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM10" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM10" t="str">
-        <v>1</v>
-      </c>
       <c r="AN10" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP10" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO10" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ10" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR10" t="str">
+      <c r="AS10" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS10" t="str">
+      <c r="AT10" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU10" t="str">
+      <c r="AV10" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV10" t="str">
+      <c r="AW10" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1792,27 +1813,30 @@
         <v>TRUE</v>
       </c>
       <c r="AL11" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM11" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM11" t="str">
-        <v>1</v>
-      </c>
       <c r="AN11" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP11" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ11" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR11" t="str">
+      <c r="AS11" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS11" t="str">
+      <c r="AT11" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU11" t="str">
+      <c r="AV11" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV11" t="str">
+      <c r="AW11" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -1926,27 +1950,30 @@
         <v>TRUE</v>
       </c>
       <c r="AL12" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM12" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM12" t="str">
-        <v>1</v>
-      </c>
       <c r="AN12" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP12" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ12" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR12" t="str">
+      <c r="AS12" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS12" t="str">
+      <c r="AT12" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU12" t="str">
+      <c r="AV12" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV12" t="str">
+      <c r="AW12" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -2060,27 +2087,30 @@
         <v>FALSE</v>
       </c>
       <c r="AL13" t="str">
+        <v>FALSE</v>
+      </c>
+      <c r="AM13" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM13" t="str">
-        <v>1</v>
-      </c>
       <c r="AN13" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP13" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ13" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR13" t="str">
+      <c r="AS13" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS13" t="str">
+      <c r="AT13" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU13" t="str">
+      <c r="AV13" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV13" t="str">
+      <c r="AW13" t="str">
         <v>Bilateral</v>
       </c>
     </row>
@@ -2194,33 +2224,36 @@
         <v>TRUE</v>
       </c>
       <c r="AL14" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="AM14" t="str">
         <v>Zapit</v>
       </c>
-      <c r="AM14" t="str">
-        <v>1</v>
-      </c>
       <c r="AN14" t="str">
-        <v>30</v>
-      </c>
-      <c r="AP14" t="str">
+        <v>1</v>
+      </c>
+      <c r="AO14" t="str">
+        <v>30</v>
+      </c>
+      <c r="AQ14" t="str">
         <v>Sound</v>
       </c>
-      <c r="AR14" t="str">
+      <c r="AS14" t="str">
         <v>Feedback</v>
       </c>
-      <c r="AS14" t="str">
+      <c r="AT14" t="str">
         <v>Inter_Trial_Interval</v>
       </c>
-      <c r="AU14" t="str">
+      <c r="AV14" t="str">
         <v>PPC</v>
       </c>
-      <c r="AV14" t="str">
+      <c r="AW14" t="str">
         <v>Bilateral</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AW14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AX14"/>
   </ignoredErrors>
 </worksheet>
 </file>